--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L219"/>
+  <dimension ref="A1:M219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -660,6 +660,11 @@
           <t>상태</t>
         </is>
       </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>상태_근거</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -704,12 +709,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -719,7 +724,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -766,12 +776,12 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -781,7 +791,12 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -828,12 +843,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -843,7 +858,12 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -890,12 +910,12 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -905,7 +925,12 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -952,12 +977,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -965,9 +990,14 @@
           <t>GA 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1044,12 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE 광고비</t>
+          <t>AGENCY_AD_PERFORMANCE.AD_COST</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS(광고비 컬럼 3종)</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -1027,9 +1057,14 @@
           <t>GA 광고비 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%)</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1111,12 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE 광고비</t>
+          <t>AGENCY_AD_PERFORMANCE.AD_COST</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS(광고비 컬럼 3종)</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1091,7 +1126,12 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%)</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1178,12 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE 광고비</t>
+          <t>AGENCY_AD_PERFORMANCE.AD_COST</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS(광고비 컬럼 3종)</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1151,9 +1191,14 @@
           <t>GA 광고비 / GA 개발 건</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%)</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1245,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE</t>
+          <t>AGENCY_AD_PERFORMANCE.CLICK_CNT</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>DGT_AD_CMPGN_DTLS(클릭)</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1213,9 +1258,14 @@
           <t>(광고 클릭수 / 광고 노출수) * 100</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 173,825/243,545 (71.4%)</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1312,12 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT(전환 이벤트)</t>
+          <t>AGENCY_AD_PERFORMANCE.CONV_MEMBER_CNT</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>BRONZE_GA4.events_YYYYMMDD</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1275,9 +1325,14 @@
           <t>(광고 전환수 / 광고 클릭수) * 100</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 45,823/243,545 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -1324,18 +1379,23 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_CREATIVE</t>
+          <t>AGENCY_AD_CREATIVE.MEDIA_CHANNEL_NM</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1442,12 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_CREATIVE</t>
+          <t>AGENCY_AD_CREATIVE.MEDIA_CHANNEL_NM</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1395,9 +1455,14 @@
           <t>YOUTUBE, KBS, 당근 등 광고를 송출하는 플랫폼</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1444,18 +1509,23 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_CREATIVE</t>
+          <t>AGENCY_AD_CREATIVE.MEDIA_CHANNEL_NM</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1502,18 +1572,23 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_CREATIVE</t>
+          <t>AGENCY_AD_CREATIVE.MEDIA_CHANNEL_NM</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1635,12 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1573,9 +1648,14 @@
           <t>1) 국내 2) 해외 3) 전체 4) 통합</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1702,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -1635,9 +1715,14 @@
           <t>1) 사례 2) 사업 3) 굿즈 4) 통합</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1769,12 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -1697,9 +1782,14 @@
           <t>1) 국내 사례 2) 국내 사업 3) 해외 사례 4) 해외 굿즈 5) 전체 굿즈 6) 통합</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1746,18 +1836,23 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -1804,18 +1899,23 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -1862,18 +1962,23 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_CREATIVE</t>
+          <t>AGENCY_AD_CREATIVE.MEDIA_CHANNEL_NM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1920,18 +2025,23 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_CREATIVE</t>
+          <t>AGENCY_AD_CREATIVE.MEDIA_CHANNEL_NM</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -1978,18 +2088,23 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_CREATIVE</t>
+          <t>AGENCY_AD_CREATIVE.MEDIA_CHANNEL_NM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -2036,18 +2151,23 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE</t>
+          <t>AGENCY_AD_PERFORMANCE.IMPRESSION_CNT</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>DGT_AD_CMPGN_DTLS(노출)</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 196,572/243,545 (80.7%)</t>
         </is>
       </c>
     </row>
@@ -2094,18 +2214,23 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE</t>
+          <t>AGENCY_AD_PERFORMANCE.CLICK_CNT</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>DGT_AD_CMPGN_DTLS(클릭)</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 173,825/243,545 (71.4%)</t>
         </is>
       </c>
     </row>
@@ -2152,18 +2277,23 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE</t>
+          <t>AGENCY_AD_PERFORMANCE.INBOUND_CALL_CNT</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>REBRDC/VIDEO_AD_CMPGN_DTLS</t>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 21,455/243,545 (8.8%)</t>
         </is>
       </c>
     </row>
@@ -2211,9 +2341,14 @@
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2261,9 +2396,14 @@
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2310,18 +2450,23 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2513,12 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -2381,9 +2526,14 @@
           <t>회원이 최초가입 시 가입캠페인</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2580,12 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -2443,9 +2593,14 @@
           <t>회원의 최종중단일자</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2647,12 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -2505,9 +2660,14 @@
           <t>회원이 최종중단 시 최종캠페인</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2555,9 +2715,14 @@
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2605,9 +2770,14 @@
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2655,9 +2825,14 @@
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr"/>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -2704,12 +2879,12 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.SPNSR_DSCNTC_DE</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -2719,7 +2894,12 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%)</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2946,12 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING(PAY_STAT_CD=F∪NULL)</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_STAT_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -2779,9 +2959,14 @@
           <t>회원번호 기준, 회원상태가 미납인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -2826,16 +3011,29 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -2882,12 +3080,12 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_AMT_CHANGE(RDCAMT_YN='Y')</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_IRSD.SPNSR_AMT·RDCAMT_YN</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -2895,9 +3093,14 @@
           <t>회원번호 기준, 후원사업(세부캠페인)별 총 감액 건 ( = 전체 감액금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -2944,18 +3147,23 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3002,18 +3210,23 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3060,18 +3273,23 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3118,18 +3336,23 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3176,18 +3399,23 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3234,18 +3462,23 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3290,16 +3523,29 @@
           <t>SV metric — 분자: MONTH_END_ACTIVE_CNT / 분모: YEAR_START_ACTIVE_CNT + DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3592,12 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -3361,7 +3607,12 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -3406,16 +3657,29 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD) + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -3462,18 +3726,23 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3518,16 +3787,29 @@
           <t>FMM.YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
           <t>전년도 연도말 활동회원 건수</t>
         </is>
       </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -3575,9 +3857,14 @@
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="3" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3624,12 +3911,12 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -3637,9 +3924,14 @@
           <t>활동, 미납1~미납5까지의 회원 포함</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -3684,16 +3976,29 @@
           <t>FMM.MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
         </is>
       </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -3738,12 +4043,25 @@
           <t>FMM.PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -3790,12 +4108,12 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.SPNSR_DSCNTC_DE</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -3805,7 +4123,12 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%)</t>
         </is>
       </c>
     </row>
@@ -3852,12 +4175,12 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.SPNSR_DSCNTC_DE</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
@@ -3867,7 +4190,12 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%)</t>
         </is>
       </c>
     </row>
@@ -3914,12 +4242,12 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.SPNSR_DSCNTC_DE</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -3929,7 +4257,12 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%)</t>
         </is>
       </c>
     </row>
@@ -3976,12 +4309,12 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.SPNSR_DSCNTC_DE</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
@@ -3991,7 +4324,12 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%)</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4376,12 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.SPNSR_DSCNTC_DE</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
@@ -4053,7 +4391,12 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%)</t>
         </is>
       </c>
     </row>
@@ -4105,9 +4448,14 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치)</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -4159,9 +4507,14 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치) / (전주/전월/전년 수치) * 100</t>
         </is>
       </c>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -4206,16 +4559,29 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
           <t>활동회원 건 / 활동회원 명</t>
         </is>
       </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4633,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
@@ -4277,7 +4643,12 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4700,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
@@ -4339,7 +4710,12 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4767,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
@@ -4401,7 +4777,12 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4834,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
@@ -4463,7 +4844,12 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -4515,13 +4901,18 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr"/>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 35,433,287/40,054,883 (88.5%)</t>
         </is>
       </c>
     </row>
@@ -4573,9 +4964,14 @@
           <t>정기회원이 정기후원사업 외 비지정(기타, 국내사업, 해외사업)으로 납부하는 일시회비</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -4627,9 +5023,14 @@
           <t>일시회원이 납부하는 회비</t>
         </is>
       </c>
-      <c r="L72" s="4" t="inlineStr">
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -4681,13 +5082,18 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr"/>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -4739,13 +5145,18 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr"/>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -4797,13 +5208,18 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.RQEST_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr"/>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 37,148,524/40,054,883 (92.7%)</t>
         </is>
       </c>
     </row>
@@ -4855,9 +5271,14 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -4909,9 +5330,14 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -4963,9 +5389,14 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="L78" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -5017,9 +5448,14 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5502,12 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING(PAY_STAT_CD=F∪NULL)</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_STAT_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -5079,9 +5515,14 @@
           <t>미납(건) / 활동(건)</t>
         </is>
       </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5569,12 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING(PAY_STAT_CD=F∪NULL)</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_STAT_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
@@ -5141,9 +5582,14 @@
           <t>신규미납(건) / 신규활동(건)</t>
         </is>
       </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5190,12 +5636,12 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING(PAY_STAT_CD=F∪NULL)</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_STAT_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -5203,9 +5649,14 @@
           <t>기존미납(건) / 기존활동(건)</t>
         </is>
       </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5703,12 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING(PAY_STAT_CD=F∪NULL)</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_STAT_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
@@ -5265,9 +5716,14 @@
           <t>후원사업 미납(건) / 후원사업 활동(건)</t>
         </is>
       </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5319,9 +5775,14 @@
           <t>(월초미납명수 − 월말미납명수) / 월초미납명수</t>
         </is>
       </c>
-      <c r="L84" s="4" t="inlineStr">
+      <c r="L84" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -5373,9 +5834,14 @@
           <t>납입회원(명) / 미납서비스 클릭회원(명) * 100</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="L85" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>추정: identity 브리지 의존</t>
         </is>
       </c>
     </row>
@@ -5422,12 +5888,12 @@
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE (또는 CRM_CODE MM005)</t>
+          <t>CRM_CODE.DTL_CD_ID</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
@@ -5435,9 +5901,14 @@
           <t>CRM &gt; 회원요약정보 &gt; 회비내역 &gt; 미납/환급정보 &gt; 미납내역</t>
         </is>
       </c>
-      <c r="L86" s="4" t="inlineStr">
+      <c r="L86" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -5482,16 +5953,29 @@
           <t>FMM.CAMPAIGN_UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr"/>
-      <c r="J87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
           <t>캠페인별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5543,9 +6027,14 @@
           <t>회원상태별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L88" s="4" t="inlineStr">
+      <c r="L88" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -5592,12 +6081,12 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER(MBER_NO distinct)</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>TD_MS_*_SNDNG_DTLS</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
@@ -5605,9 +6094,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L89" s="4" t="inlineStr">
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,470,780/38,470,780 (100%)</t>
         </is>
       </c>
     </row>
@@ -5654,12 +6148,12 @@
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_RESULT(성공)</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>TD_MS_EMAIL_LQY_SNDNG / TD_MS_MSG_AT_LQY_SNDNG / TD_MS_PSTMTR_LQY_SNDNG</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
@@ -5667,9 +6161,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5716,12 +6215,12 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_RESULT(실패)</t>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>TD_MS_*_LQY_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
@@ -5729,9 +6228,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.FAIL_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5778,12 +6282,12 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY(LETTER)</t>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>TM_RM_RELATNSP_LETTER_INFO</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -5791,9 +6295,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5841,9 +6350,14 @@
       <c r="I93" s="3" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr"/>
       <c r="K93" s="3" t="inlineStr"/>
-      <c r="L93" s="4" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -5888,16 +6402,29 @@
           <t>FSE.GIFT_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5944,18 +6471,23 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY.GFTMNEY</t>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>TM_RM_RELATNSP_GFTMNEY_INFO.GFTMNEY</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.GIFT_PART_AMT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6003,9 +6535,14 @@
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr"/>
       <c r="K96" s="3" t="inlineStr"/>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L96" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6053,9 +6590,14 @@
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr"/>
       <c r="K97" s="3" t="inlineStr"/>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="L97" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6103,9 +6645,14 @@
       <c r="I98" s="3" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr"/>
       <c r="K98" s="3" t="inlineStr"/>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="L98" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6153,9 +6700,14 @@
       <c r="I99" s="3" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr"/>
       <c r="K99" s="3" t="inlineStr"/>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="L99" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6203,9 +6755,14 @@
       <c r="I100" s="3" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr"/>
       <c r="K100" s="3" t="inlineStr"/>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="L100" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6252,18 +6809,19 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT.ga_session_id</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(event_params: ga_session_id)</t>
-        </is>
-      </c>
+          <t>GA4_EVENT.GA_SESSION_ID</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr"/>
       <c r="K101" s="3" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_GA_BEHAVIOR.SESSION_CNT` 비영 68,836/68,836 (100%)</t>
         </is>
       </c>
     </row>
@@ -6310,18 +6868,19 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT + IDENTITY_MEMBER_XREF</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events_YYYYMMDD</t>
-        </is>
-      </c>
+          <t>GA4_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr"/>
       <c r="K102" s="3" t="inlineStr"/>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_GA_BEHAVIOR.AVG_SESSION_DURATION` 전건 NULL</t>
         </is>
       </c>
     </row>
@@ -6368,22 +6927,23 @@
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(event_params)</t>
-        </is>
-      </c>
+          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="3" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="L103" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6430,22 +6990,23 @@
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(event_params)</t>
-        </is>
-      </c>
+          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr"/>
       <c r="K104" s="3" t="inlineStr">
         <is>
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
         </is>
       </c>
-      <c r="L104" s="5" t="inlineStr">
+      <c r="L104" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6492,22 +7053,23 @@
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM</t>
-        </is>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(event_params)</t>
-        </is>
-      </c>
+          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr"/>
       <c r="K105" s="3" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L105" s="5" t="inlineStr">
+      <c r="L105" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6554,12 +7116,12 @@
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
@@ -6567,9 +7129,14 @@
           <t>2024 기념일 캠페인 / 2024 ACL 등</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="L106" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6616,22 +7183,23 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE</t>
-        </is>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(traffic_source)</t>
-        </is>
-      </c>
+          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="3" t="inlineStr">
         <is>
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
         </is>
       </c>
-      <c r="L107" s="5" t="inlineStr">
+      <c r="L107" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6678,18 +7246,19 @@
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE</t>
-        </is>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(traffic_source)</t>
-        </is>
-      </c>
+          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr"/>
       <c r="K108" s="3" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="L108" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6737,9 +7306,14 @@
       <c r="I109" s="3" t="inlineStr"/>
       <c r="J109" s="3" t="inlineStr"/>
       <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="L109" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6791,9 +7365,14 @@
           <t>예) https://m.goodneighbors.kr/campaign/turn25b</t>
         </is>
       </c>
-      <c r="L110" s="5" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -6840,18 +7419,19 @@
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT.percent_scrolled</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(event_params: percent_scrolled)</t>
-        </is>
-      </c>
+          <t>GA4_EVENT.PERCENT_SCROLLED</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr"/>
       <c r="K111" s="3" t="inlineStr"/>
-      <c r="L111" s="5" t="inlineStr">
+      <c r="L111" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_GA_BEHAVIOR.SCROLL_DEPTH` 비영 14,042/68,836 (20.4%)</t>
         </is>
       </c>
     </row>
@@ -6898,18 +7478,19 @@
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT + IDENTITY_MEMBER_XREF</t>
-        </is>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events_YYYYMMDD</t>
-        </is>
-      </c>
+          <t>GA4_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr"/>
       <c r="K112" s="3" t="inlineStr"/>
-      <c r="L112" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_GA_BEHAVIOR.BOUNCE_RATE` 전건 NULL</t>
         </is>
       </c>
     </row>
@@ -6956,18 +7537,19 @@
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE</t>
-        </is>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>BRONZE_GA4.events(traffic_source)</t>
-        </is>
-      </c>
+          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr"/>
       <c r="K113" s="3" t="inlineStr"/>
-      <c r="L113" s="5" t="inlineStr">
+      <c r="L113" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -7014,18 +7596,23 @@
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER + GA4_IDENTITY</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO + BRONZE_GA4.events</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr"/>
-      <c r="L114" s="4" t="inlineStr">
+      <c r="L114" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7072,18 +7659,23 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER + GA4_IDENTITY</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO + BRONZE_GA4.events</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr"/>
-      <c r="L115" s="4" t="inlineStr">
+      <c r="L115" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7130,18 +7722,23 @@
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER + GA4_IDENTITY</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO + BRONZE_GA4.events</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr"/>
-      <c r="L116" s="5" t="inlineStr">
+      <c r="L116" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>추정: GA4 계통(G-5 샤드 부분입고)</t>
         </is>
       </c>
     </row>
@@ -7188,12 +7785,12 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
@@ -7201,9 +7798,14 @@
           <t>신규: 당해년도 개발, 기존: 당해년도 이전 개발</t>
         </is>
       </c>
-      <c r="L117" s="4" t="inlineStr">
+      <c r="L117" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7852,7 @@
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>CRM_ORG</t>
+          <t>CRM_ORG.DEPT_ID</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
@@ -7259,9 +7861,14 @@
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr"/>
-      <c r="L118" s="4" t="inlineStr">
+      <c r="L118" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7915,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>CRM_ORG</t>
+          <t>CRM_ORG.DEPT_ID</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -7317,9 +7924,14 @@
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr"/>
-      <c r="L119" s="4" t="inlineStr">
+      <c r="L119" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7978,7 @@
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>CRM_ORG</t>
+          <t>CRM_ORG.DEPT_ID</t>
         </is>
       </c>
       <c r="J120" s="3" t="inlineStr">
@@ -7375,9 +7987,14 @@
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr">
+      <c r="L120" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7424,18 +8041,23 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr">
+      <c r="L121" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7482,18 +8104,23 @@
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr">
+      <c r="L122" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7540,18 +8167,23 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr">
+      <c r="L123" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7598,18 +8230,23 @@
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr"/>
-      <c r="L124" s="4" t="inlineStr">
+      <c r="L124" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7657,9 +8294,14 @@
       <c r="I125" s="3" t="inlineStr"/>
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="3" t="inlineStr"/>
-      <c r="L125" s="4" t="inlineStr">
+      <c r="L125" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7706,12 +8348,12 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER + GA4_IDENTITY</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO + BRONZE_GA4.events</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
@@ -7719,9 +8361,14 @@
           <t>"페이지 경로+쿼리 문자열"에서 파생. URL에서 childnum= 뒤에 오는 13자리. 예) https://gni.kr/url/25acl_25ABC.gn?memnum=1831636&amp;childnum=CMR-0102-002758 → 결연아동코드 = CMR-0102-002758</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="L126" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>추정: identity 브리지 의존</t>
         </is>
       </c>
     </row>
@@ -7768,7 +8415,7 @@
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr">
@@ -7777,9 +8424,14 @@
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr"/>
-      <c r="L127" s="4" t="inlineStr">
+      <c r="L127" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7826,7 +8478,7 @@
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr">
@@ -7839,9 +8491,14 @@
           <t>국내사단(국내아동권리보호사업(사단법인), 결식아동지원, 아동학대예방, 저소득가정지원), 국내사복(국내아동권리보호사업(사회복지법인), 국내사업, 좋은이웃(사복)), 결연(해외아동결연), 해외구호(희망학교지원사업, 해외교육지원사업, 보건의료지원사업, 식수위생지원사업, 재난구호지원사업, 해외지역개발지원사업), 기타(대북지원사업, 좋은이웃, 전체사업지원)</t>
         </is>
       </c>
-      <c r="L128" s="4" t="inlineStr">
+      <c r="L128" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7888,18 +8545,23 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_CD</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_SETLE_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr"/>
-      <c r="L129" s="4" t="inlineStr">
+      <c r="L129" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -7946,18 +8608,23 @@
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_CD</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_SETLE_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr"/>
-      <c r="L130" s="4" t="inlineStr">
+      <c r="L130" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8005,9 +8672,14 @@
       <c r="I131" s="3" t="inlineStr"/>
       <c r="J131" s="3" t="inlineStr"/>
       <c r="K131" s="3" t="inlineStr"/>
-      <c r="L131" s="4" t="inlineStr">
+      <c r="L131" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8055,9 +8727,14 @@
       <c r="I132" s="3" t="inlineStr"/>
       <c r="J132" s="3" t="inlineStr"/>
       <c r="K132" s="3" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr">
+      <c r="L132" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8105,9 +8782,14 @@
       <c r="I133" s="3" t="inlineStr"/>
       <c r="J133" s="3" t="inlineStr"/>
       <c r="K133" s="3" t="inlineStr"/>
-      <c r="L133" s="4" t="inlineStr">
+      <c r="L133" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8154,18 +8836,23 @@
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr">
+      <c r="L134" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8212,18 +8899,23 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
-      <c r="L135" s="4" t="inlineStr">
+      <c r="L135" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8270,18 +8962,23 @@
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER (+ STATUS_HIST)</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO / TH_MM_FDRM_MBER_STNG_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr"/>
-      <c r="L136" s="4" t="inlineStr">
+      <c r="L136" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8328,18 +9025,23 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>SND_REQ_MST (SEND_GBN_TOP/MID/BOT)</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr"/>
-      <c r="L137" s="4" t="inlineStr">
+      <c r="L137" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8386,18 +9088,23 @@
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>SND_REQ_MST (SEND_GBN_TOP/MID/BOT)</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr"/>
-      <c r="L138" s="4" t="inlineStr">
+      <c r="L138" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8444,18 +9151,23 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>SND_REQ_MST (SEND_GBN_TOP/MID/BOT)</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr"/>
-      <c r="L139" s="4" t="inlineStr">
+      <c r="L139" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8503,9 +9215,14 @@
       <c r="I140" s="3" t="inlineStr"/>
       <c r="J140" s="3" t="inlineStr"/>
       <c r="K140" s="3" t="inlineStr"/>
-      <c r="L140" s="4" t="inlineStr">
+      <c r="L140" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8550,20 +9267,17 @@
           <t>DIM_DATE</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>(ETL 생성)</t>
-        </is>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>(원천 무관)</t>
-        </is>
-      </c>
+      <c r="I141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr"/>
       <c r="K141" s="3" t="inlineStr"/>
-      <c r="L141" s="4" t="inlineStr">
+      <c r="L141" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8611,9 +9325,14 @@
       <c r="I142" s="3" t="inlineStr"/>
       <c r="J142" s="3" t="inlineStr"/>
       <c r="K142" s="3" t="inlineStr"/>
-      <c r="L142" s="4" t="inlineStr">
+      <c r="L142" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8661,9 +9380,14 @@
       <c r="I143" s="3" t="inlineStr"/>
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="3" t="inlineStr"/>
-      <c r="L143" s="4" t="inlineStr">
+      <c r="L143" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8711,9 +9435,14 @@
       <c r="I144" s="3" t="inlineStr"/>
       <c r="J144" s="3" t="inlineStr"/>
       <c r="K144" s="3" t="inlineStr"/>
-      <c r="L144" s="4" t="inlineStr">
+      <c r="L144" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8761,9 +9490,14 @@
       <c r="I145" s="3" t="inlineStr"/>
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="3" t="inlineStr"/>
-      <c r="L145" s="4" t="inlineStr">
+      <c r="L145" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8811,9 +9545,14 @@
       <c r="I146" s="3" t="inlineStr"/>
       <c r="J146" s="3" t="inlineStr"/>
       <c r="K146" s="3" t="inlineStr"/>
-      <c r="L146" s="4" t="inlineStr">
+      <c r="L146" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8861,9 +9600,14 @@
       <c r="I147" s="3" t="inlineStr"/>
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="3" t="inlineStr"/>
-      <c r="L147" s="4" t="inlineStr">
+      <c r="L147" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8911,9 +9655,14 @@
       <c r="I148" s="3" t="inlineStr"/>
       <c r="J148" s="3" t="inlineStr"/>
       <c r="K148" s="3" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr">
+      <c r="L148" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -8961,9 +9710,14 @@
       <c r="I149" s="3" t="inlineStr"/>
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="3" t="inlineStr"/>
-      <c r="L149" s="4" t="inlineStr">
+      <c r="L149" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9011,9 +9765,14 @@
       <c r="I150" s="3" t="inlineStr"/>
       <c r="J150" s="3" t="inlineStr"/>
       <c r="K150" s="3" t="inlineStr"/>
-      <c r="L150" s="4" t="inlineStr">
+      <c r="L150" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9060,18 +9819,23 @@
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>TM_CM_CMPGN_MNG (+BRND_MNG+MKTNG_CMPGN_MNG)</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
-      <c r="L151" s="4" t="inlineStr">
+      <c r="L151" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9118,18 +9882,23 @@
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV(MBER_NO distinct)</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.MBER_NO</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr"/>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -9176,18 +9945,23 @@
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -9234,18 +10008,23 @@
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_AMT_CHANGE(RDCAMT_YN='N')</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_IRSD.SPNSR_AMT·RDCAMT_YN</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr"/>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L154" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9290,12 +10069,25 @@
           <t>FME→FMM.INCREASE_CNT</t>
         </is>
       </c>
-      <c r="I155" s="3" t="inlineStr"/>
-      <c r="J155" s="3" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K155" s="3" t="inlineStr"/>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9348,6 +10140,11 @@
           <t>WAIT</t>
         </is>
       </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>추정: 원천 미입고 계통(E-6 등)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -9398,6 +10195,11 @@
           <t>WAIT</t>
         </is>
       </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>추정: 원천 미입고 계통(E-6 등)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -9448,6 +10250,11 @@
           <t>WAIT</t>
         </is>
       </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>추정: 원천 미입고 계통(E-6 등)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -9498,6 +10305,11 @@
           <t>WAIT</t>
         </is>
       </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>추정: 원천 미입고 계통(E-6 등)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -9542,18 +10354,23 @@
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_STATUS_HIST + CRM_MEMBER_SPONSOR_BIZ</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>TH_MM_FDRM_MBER_STNG_DTLS + TM_MM_FDRM_MBER_SPNSR_BSNS</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr"/>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9598,12 +10415,25 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I161" s="3" t="inlineStr"/>
-      <c r="J161" s="3" t="inlineStr"/>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K161" s="3" t="inlineStr"/>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9651,9 +10481,14 @@
       <c r="I162" s="3" t="inlineStr"/>
       <c r="J162" s="3" t="inlineStr"/>
       <c r="K162" s="3" t="inlineStr"/>
-      <c r="L162" s="4" t="inlineStr">
+      <c r="L162" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9698,12 +10533,25 @@
           <t>FMM.ACTIVE_CUM_CNT</t>
         </is>
       </c>
-      <c r="I163" s="3" t="inlineStr"/>
-      <c r="J163" s="3" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K163" s="3" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9751,9 +10599,14 @@
       <c r="I164" s="3" t="inlineStr"/>
       <c r="J164" s="3" t="inlineStr"/>
       <c r="K164" s="3" t="inlineStr"/>
-      <c r="L164" s="4" t="inlineStr">
+      <c r="L164" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9801,9 +10654,14 @@
       <c r="I165" s="3" t="inlineStr"/>
       <c r="J165" s="3" t="inlineStr"/>
       <c r="K165" s="3" t="inlineStr"/>
-      <c r="L165" s="4" t="inlineStr">
+      <c r="L165" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9850,18 +10708,23 @@
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE (또는 CRM_CODE MM005)</t>
+          <t>CRM_CODE.DTL_CD_ID</t>
         </is>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr"/>
-      <c r="L166" s="4" t="inlineStr">
+      <c r="L166" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9913,9 +10776,14 @@
           <t>캠페인 가입 이후 납입하는 회비</t>
         </is>
       </c>
-      <c r="L167" s="4" t="inlineStr">
+      <c r="L167" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -9967,9 +10835,14 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 개월수</t>
         </is>
       </c>
-      <c r="L168" s="4" t="inlineStr">
+      <c r="L168" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10021,9 +10894,14 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 년수</t>
         </is>
       </c>
-      <c r="L169" s="4" t="inlineStr">
+      <c r="L169" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10070,12 +10948,12 @@
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV(MBER_NO distinct)</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.MBER_NO</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
@@ -10085,7 +10963,12 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -10137,9 +11020,14 @@
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
         </is>
       </c>
-      <c r="L171" s="4" t="inlineStr">
+      <c r="L171" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10191,9 +11079,14 @@
           <t>N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수</t>
         </is>
       </c>
-      <c r="L172" s="4" t="inlineStr">
+      <c r="L172" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10245,9 +11138,14 @@
           <t>(N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수) × 100</t>
         </is>
       </c>
-      <c r="L173" s="4" t="inlineStr">
+      <c r="L173" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10299,9 +11197,14 @@
           <t>평균 납입회비 × 평균 활동 기간</t>
         </is>
       </c>
-      <c r="L174" s="4" t="inlineStr">
+      <c r="L174" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10353,9 +11256,14 @@
           <t>광고비(편성비) 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L175" s="5" t="inlineStr">
+      <c r="L175" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>추정: AGENCY 계통(연결키 Q10 대기)</t>
         </is>
       </c>
     </row>
@@ -10402,12 +11310,12 @@
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>(원천 부재)</t>
+          <t>ERP_BUDGET.EXEC_AMT</t>
         </is>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>(ERP 원장에 없음)</t>
+          <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
@@ -10415,9 +11323,14 @@
           <t>ERP 모금성 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L176" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="L176" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_BUDGET.FUNDRAISING_COST` 전건 NULL</t>
         </is>
       </c>
     </row>
@@ -10469,7 +11382,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr">
@@ -10479,7 +11392,12 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -10531,9 +11449,14 @@
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
         </is>
       </c>
-      <c r="L178" s="4" t="inlineStr">
+      <c r="L178" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10585,9 +11508,14 @@
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
         </is>
       </c>
-      <c r="L179" s="4" t="inlineStr">
+      <c r="L179" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10639,9 +11567,14 @@
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
         </is>
       </c>
-      <c r="L180" s="4" t="inlineStr">
+      <c r="L180" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10693,9 +11626,14 @@
           <t>캠페인별 중단(건) / (캠페인별 개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L181" s="4" t="inlineStr">
+      <c r="L181" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10747,9 +11685,14 @@
           <t>조회시점 기준 캠페인 중단(건) / (캠페인 개발(건) + 캠페인 전월말활동회원(건))</t>
         </is>
       </c>
-      <c r="L182" s="4" t="inlineStr">
+      <c r="L182" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10801,9 +11744,14 @@
           <t>캠페인별 누계중단(건) / (캠페인별 누계개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L183" s="4" t="inlineStr">
+      <c r="L183" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10855,9 +11803,14 @@
           <t>조회시점 기준 캠페인 누계중단(건) / 캠페인별 누계개발(건)</t>
         </is>
       </c>
-      <c r="L184" s="4" t="inlineStr">
+      <c r="L184" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10909,9 +11862,14 @@
           <t>캠페인별 납입방식 중단(건) / (캠페인별 납입방식 개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L185" s="4" t="inlineStr">
+      <c r="L185" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -10958,12 +11916,12 @@
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE + CRM_MEMBER_AMT_CHANGE</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC + TM_MM_FDRM_MBER_IRSD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr">
@@ -10971,9 +11929,14 @@
           <t>후원취소 및 감액한 후원사업의 금액 / 10,000</t>
         </is>
       </c>
-      <c r="L186" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L186" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11025,9 +11988,14 @@
           <t>캠페인별 이탈(건) / 캠페인별 개발(건)</t>
         </is>
       </c>
-      <c r="L187" s="4" t="inlineStr">
+      <c r="L187" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11079,9 +12047,14 @@
           <t>캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L188" s="4" t="inlineStr">
+      <c r="L188" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11133,9 +12106,14 @@
           <t>조회시점 기준 캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L189" s="4" t="inlineStr">
+      <c r="L189" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11187,9 +12165,14 @@
           <t>캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L190" s="4" t="inlineStr">
+      <c r="L190" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11241,9 +12224,14 @@
           <t>조회시점 기준 캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L191" s="4" t="inlineStr">
+      <c r="L191" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11295,9 +12283,14 @@
           <t>캠페인별 납입회비 / 총 납입회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L192" s="4" t="inlineStr">
+      <c r="L192" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11349,9 +12342,14 @@
           <t>캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L193" s="4" t="inlineStr">
+      <c r="L193" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11403,9 +12401,14 @@
           <t>조회시점 기준 캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L194" s="4" t="inlineStr">
+      <c r="L194" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11457,9 +12460,14 @@
           <t>캠페인별 미납회비 / 총 미납회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L195" s="4" t="inlineStr">
+      <c r="L195" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11506,12 +12514,12 @@
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER(MBER_NO distinct)</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>TD_MS_*_SNDNG_DTLS</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
@@ -11519,9 +12527,14 @@
           <t>서비스별 발송수(명) / 전체회원수(명) × 100</t>
         </is>
       </c>
-      <c r="L196" s="4" t="inlineStr">
+      <c r="L196" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,470,780/38,470,780 (100%)</t>
         </is>
       </c>
     </row>
@@ -11568,12 +12581,12 @@
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>CRM_SEND_RESULT(성공)</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>TD_MS_EMAIL_LQY_SNDNG / TD_MS_MSG_AT_LQY_SNDNG / TD_MS_PSTMTR_LQY_SNDNG</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
@@ -11581,9 +12594,14 @@
           <t>발송성공수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L197" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L197" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11635,9 +12653,14 @@
           <t>클릭수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L198" s="5" t="inlineStr">
+      <c r="L198" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>추정: identity 브리지 의존</t>
         </is>
       </c>
     </row>
@@ -11684,12 +12707,12 @@
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV(MBER_NO distinct)</t>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_DVLP_AMT.MBER_NO</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
@@ -11697,9 +12720,14 @@
           <t>개발회원(명) / 서비스 클릭수(명) × 100</t>
         </is>
       </c>
-      <c r="L199" s="5" t="inlineStr">
+      <c r="L199" s="4" t="inlineStr">
         <is>
           <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%)</t>
         </is>
       </c>
     </row>
@@ -11751,9 +12779,14 @@
           <t>(증액 회원수(명,건) / 서비스별 발송 성공회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L200" s="4" t="inlineStr">
+      <c r="L200" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11805,9 +12838,14 @@
           <t>(서비스별 증액 후 N개월 시점 유지 회원(명,건) / 서비스별 증액 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L201" s="4" t="inlineStr">
+      <c r="L201" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11859,9 +12897,14 @@
           <t>(서비스별 발송 후 N개월 시점 유지 회원(명,건) / 서비스별 참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L202" s="4" t="inlineStr">
+      <c r="L202" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11913,9 +12956,14 @@
           <t>(서비스별 증액회원 중 납입회원(명,건) / 서비스별 증액회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 증액회원의 납입회비) / 서비스별 증액회원(명)</t>
         </is>
       </c>
-      <c r="L203" s="4" t="inlineStr">
+      <c r="L203" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -11967,9 +13015,14 @@
           <t>(서비스별 참여회원 중 납입회원(명,건) / 서비스별 참여회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 참여회원의 납입회비) / 서비스별 참여회원(명)</t>
         </is>
       </c>
-      <c r="L204" s="4" t="inlineStr">
+      <c r="L204" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12021,9 +13074,14 @@
           <t>(서비스별 증액회원 중 중단회원(명,건) / 서비스별 증액회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L205" s="4" t="inlineStr">
+      <c r="L205" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12075,9 +13133,14 @@
           <t>(서비스별 참여회원 중 중단회원(명,건) / 서비스별 참여회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L206" s="4" t="inlineStr">
+      <c r="L206" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12129,9 +13192,14 @@
           <t>(해당 캠페인 서비스별 증액회원(명,건) / 서비스별 전체 증액회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L207" s="4" t="inlineStr">
+      <c r="L207" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12183,9 +13251,14 @@
           <t>(해당 캠페인 서비스별 참여회원(명,건) / 서비스별 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L208" s="4" t="inlineStr">
+      <c r="L208" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12237,9 +13310,14 @@
           <t>(해당 서비스·캠페인 조합에서 N개월 시점 유지 회원(명,건) / 해당 캠페인 가입회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L209" s="4" t="inlineStr">
+      <c r="L209" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12286,12 +13364,12 @@
       </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY(LETTER)</t>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
         </is>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>TM_RM_RELATNSP_LETTER_INFO</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
@@ -12299,9 +13377,14 @@
           <t>(서비스별 서신 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L210" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L210" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -12353,9 +13436,14 @@
           <t>(서신참여 후 N개월 시점 유지 회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L211" s="4" t="inlineStr">
+      <c r="L211" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12407,9 +13495,14 @@
           <t>(서비스별 서신참여회원 중 납입회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 서신참여회원의 납입회비) / 서비스별 서신참여회원(명)</t>
         </is>
       </c>
-      <c r="L212" s="4" t="inlineStr">
+      <c r="L212" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12461,9 +13554,14 @@
           <t>(서비스별 서신참여회원 중 중단회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L213" s="4" t="inlineStr">
+      <c r="L213" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12515,9 +13613,14 @@
           <t>(해당 캠페인 서비스별 서신참여회원(명,건) / 서비스별 전체 서신참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L214" s="4" t="inlineStr">
+      <c r="L214" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12562,16 +13665,29 @@
           <t>SV metric — 분자: GIFT_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I215" s="3" t="inlineStr"/>
-      <c r="J215" s="3" t="inlineStr"/>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J215" s="3" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
           <t>(서비스별 선물금 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L215" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L215" s="6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>실측: `FACT_SERVICE_EVENT.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -12623,9 +13739,14 @@
           <t>(서비스별 선물금참여 후 N개월 시점 유지 회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L216" s="4" t="inlineStr">
+      <c r="L216" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12677,9 +13798,14 @@
           <t>(서비스별 선물금참여회원 중 납입회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 선물금참여회원의 납입회비) / 서비스별 선물금참여회원수(명)</t>
         </is>
       </c>
-      <c r="L217" s="4" t="inlineStr">
+      <c r="L217" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12731,9 +13857,14 @@
           <t>(서비스별 선물금참여회원 중 중단회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L218" s="4" t="inlineStr">
+      <c r="L218" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -12785,9 +13916,14 @@
           <t>(해당 캠페인 서비스별 선물금참여회원(명,건) / 서비스별 전체 선물금참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L219" s="4" t="inlineStr">
+      <c r="L219" s="5" t="inlineStr">
         <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음</t>
         </is>
       </c>
     </row>
@@ -13034,7 +14170,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -13206,7 +14342,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -13347,7 +14483,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -14228,13 +15364,13 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>FACT_AD_PERFORMANCE.AD_START_TIME</t>
+          <t>FACT_AD_BROADCAST.AD_START_TIME</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>필드인벤토리~</t>
         </is>
       </c>
     </row>
@@ -14320,7 +15456,7 @@
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>필드인벤토리~</t>
         </is>
       </c>
     </row>
@@ -14830,7 +15966,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>FACT_AD_PERFORMANCE.GA_CONV_CNT</t>
+          <t>FACT_AD_PERFORMANCE.GA_CONV_MEMBERS</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr"/>
@@ -15389,13 +16525,13 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -16201,7 +17337,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -16244,7 +17380,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -16291,7 +17427,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -17402,7 +18538,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -17445,7 +18581,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -17492,7 +18628,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -18325,7 +19461,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -18497,7 +19633,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -18638,7 +19774,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공3</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -20885,13 +22021,13 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.ENROLL_PATH</t>
+          <t>DIM_MEMBER.JOIN_PATH_CD</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr"/>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>필드인벤토리~</t>
         </is>
       </c>
     </row>
@@ -21014,13 +22150,13 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE</t>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr"/>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>필드인벤토리~</t>
         </is>
       </c>
     </row>
@@ -21220,18 +22356,18 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공162</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_REASON</t>
+          <t>DIM_REASON</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr"/>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -24831,13 +25967,13 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr"/>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -25695,13 +26831,13 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr"/>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -27583,13 +28719,13 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr"/>
       <c r="I265" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -30163,13 +31299,13 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H325" s="3" t="inlineStr"/>
       <c r="I325" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -30249,7 +31385,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_CHANNEL</t>
+          <t>FACT_SERVICE_EVENT.STOP_CHANNEL</t>
         </is>
       </c>
       <c r="H327" s="3" t="inlineStr"/>
@@ -31332,13 +32468,13 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H352" s="3" t="inlineStr"/>
       <c r="I352" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -31547,13 +32683,13 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H357" s="3" t="inlineStr"/>
       <c r="I357" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -32919,13 +34055,13 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H389" s="3" t="inlineStr"/>
       <c r="I389" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -33173,13 +34309,13 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H395" s="3" t="inlineStr"/>
       <c r="I395" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -34248,13 +35384,13 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER</t>
+          <t>DIM_MEMBER</t>
         </is>
       </c>
       <c r="H420" s="3" t="inlineStr"/>
       <c r="I420" s="3" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-07 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>WIDE_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -14456,7 +14456,7 @@
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>WIDE_DEV_ACHIEVEMENT.ACTUAL_CNT</t>
+          <t>FACT_DEV_ACHIEVEMENT.ACTUAL_CNT</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -17315,7 +17315,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>WIDE_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>WIDE_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -19510,7 +19510,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>WIDE_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -21247,14 +21247,10 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>공35</t>
-        </is>
-      </c>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.STOP_CNT</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -21264,7 +21260,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>교정등록부(WRONG_GRAIN)</t>
         </is>
       </c>
     </row>
@@ -21341,14 +21337,10 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>공35</t>
-        </is>
-      </c>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.STOP_CNT</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -21358,7 +21350,7 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>교정등록부(WRONG_GRAIN)</t>
         </is>
       </c>
     </row>
@@ -21435,14 +21427,10 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>공35</t>
-        </is>
-      </c>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.STOP_CNT</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -21452,7 +21440,7 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>교정등록부(WRONG_GRAIN)</t>
         </is>
       </c>
     </row>
@@ -21850,14 +21838,10 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>공4·5·149</t>
-        </is>
-      </c>
+      <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.DEV_CNT</t>
+          <t>FACT_MEMBER_EVENT.DEV_CNT</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -21867,7 +21851,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>교정등록부(WRONG_GRAIN)</t>
         </is>
       </c>
     </row>
@@ -21897,14 +21881,10 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>공4·5·149</t>
-        </is>
-      </c>
+      <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.DEV_CNT</t>
+          <t>FACT_MEMBER_EVENT.DEV_CNT</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -21914,7 +21894,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>교정등록부(WRONG_GRAIN)</t>
         </is>
       </c>
     </row>
@@ -21944,14 +21924,10 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>공4·5·149</t>
-        </is>
-      </c>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.DEV_CNT</t>
+          <t>FACT_MEMBER_EVENT.DEV_CNT</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -21961,7 +21937,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>교정등록부(WRONG_GRAIN)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr"/>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr"/>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -14177,7 +14177,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-10</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 231,012/243,545 (94.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 173,825/243,545 (71.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 45,823/243,545 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,417 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 196,572/243,545 (80.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,417 (80.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 173,825/243,545 (71.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 21,455/243,545 (8.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,070/255,417 (8.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -3012,14 +3012,14 @@
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3524,14 +3524,14 @@
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3658,14 +3658,14 @@
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -3788,14 +3788,14 @@
           <t>전년도 연도말 활동회원 건수</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 35,527,740/40,054,883 (88.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -3985,14 +3985,14 @@
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
         </is>
       </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 37,695,311/40,054,883 (94.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -4568,14 +4568,14 @@
           <t>활동회원 건 / 활동회원 명</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,839행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,470,780/38,470,780 (100.0%)</t>
+          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -6179,14 +6179,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -6246,14 +6246,14 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.FAIL_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT.FAIL_MEMBERS` 비영 1,986,871/38,467,142 (5.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -6563,7 +6563,11 @@
           <t>GA4_EVENT.EVENT_DT</t>
         </is>
       </c>
-      <c r="J96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K96" s="4" t="inlineStr"/>
       <c r="L96" s="5" t="inlineStr">
         <is>
@@ -6622,7 +6626,11 @@
           <t>GA4_EVENT.EVENT_DT</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr"/>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="5" t="inlineStr">
         <is>
@@ -6681,7 +6689,11 @@
           <t>GA4_EVENT.EVENT_DT</t>
         </is>
       </c>
-      <c r="J98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K98" s="4" t="inlineStr"/>
       <c r="L98" s="5" t="inlineStr">
         <is>
@@ -6740,7 +6752,11 @@
           <t>GA4_EVENT.EVENT_DT</t>
         </is>
       </c>
-      <c r="J99" s="4" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K99" s="4" t="inlineStr"/>
       <c r="L99" s="5" t="inlineStr">
         <is>
@@ -6799,7 +6815,11 @@
           <t>GA4_EVENT.EVENT_DT</t>
         </is>
       </c>
-      <c r="J100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="5" t="inlineStr">
         <is>
@@ -6858,7 +6878,11 @@
           <t>GA4_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr">
         <is>
@@ -6867,7 +6891,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.SESSION_CNT` 비영 68,836/68,836 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_GA_BEHAVIOR.SESSION_CNT` 비영 4,376,338/4,376,339 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6996,11 @@
           <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
@@ -6985,7 +7013,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 4,017행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7063,11 @@
           <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
@@ -7048,7 +7080,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 4,017행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7130,11 @@
           <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
@@ -7111,7 +7147,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 4,017행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7199,7 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -7178,7 +7214,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7264,11 @@
           <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
@@ -7241,7 +7281,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 147행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7331,11 @@
           <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
-      <c r="J108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="5" t="inlineStr">
         <is>
@@ -7300,7 +7344,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 147행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7508,11 @@
           <t>GA4_EVENT.PERCENT_SCROLLED</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr">
         <is>
@@ -7473,7 +7521,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.SCROLL_DEPTH` 비영 14,042/68,836 (20.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_GA_BEHAVIOR.SCROLL_DEPTH` 비영 904,700/4,376,339 (20.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7626,11 @@
           <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
-      <c r="J113" s="4" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr">
         <is>
@@ -7587,7 +7639,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 147행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8136,7 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
@@ -8095,7 +8147,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8199,7 @@
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
@@ -8158,7 +8210,7 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8262,7 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
@@ -8221,7 +8273,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8325,7 @@
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
@@ -8284,7 +8336,7 @@
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9914,7 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
@@ -9873,7 +9925,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,144행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9977,7 @@
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr"/>
@@ -9988,7 +10040,7 @@
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr"/>
@@ -10046,12 +10098,12 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr"/>
@@ -10109,12 +10161,12 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr"/>
@@ -10408,23 +10460,23 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr"/>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 38,423,125/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -10471,23 +10523,23 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -10597,12 +10649,12 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -10802,7 +10854,7 @@
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,839행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11091,7 @@
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -11530,12 +11582,12 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -11543,14 +11595,14 @@
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
         </is>
       </c>
-      <c r="L178" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -11597,12 +11649,12 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
@@ -11610,14 +11662,14 @@
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
         </is>
       </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -11664,12 +11716,12 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -11677,14 +11729,14 @@
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
         </is>
       </c>
-      <c r="L180" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11788,7 @@
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -11803,7 +11855,7 @@
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -11870,7 +11922,7 @@
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -11937,7 +11989,7 @@
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -12004,7 +12056,7 @@
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -12066,12 +12118,12 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -12133,12 +12185,12 @@
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -12535,12 +12587,12 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K193" s="4" t="inlineStr">
@@ -12602,12 +12654,12 @@
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -12669,12 +12721,12 @@
       </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K195" s="4" t="inlineStr">
@@ -12756,7 +12808,7 @@
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,470,780/38,470,780 (100.0%)</t>
+          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12803,12 +12855,12 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K197" s="4" t="inlineStr">
@@ -12816,14 +12868,14 @@
           <t>발송성공수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L197" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L197" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12986,7 @@
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr">
@@ -13586,12 +13638,12 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
@@ -14177,7 +14229,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17367,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-11</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,417 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,452 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,417 (80.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,452 (80.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,070/255,417 (8.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,078/255,452 (8.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PERCENT_SCROLLED</t>
+          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14229,7 +14229,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -15713,20 +15713,16 @@
           <t>문자</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>공13</t>
-        </is>
-      </c>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.PLATFORM_TYPE</t>
+          <t>(미매칭 — GOLD 물리·SV 대응 미확인)</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리·별칭등록부</t>
+          <t>(미매칭)</t>
         </is>
       </c>
     </row>
@@ -16017,13 +16013,13 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.DURATION_SEC</t>
+          <t>DIM_AD_CREATIVE</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -16311,20 +16307,16 @@
           <t>문자</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>(215밖)</t>
-        </is>
-      </c>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.TARGET_GROUP</t>
+          <t>(미매칭 — GOLD 물리·SV 대응 미확인)</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>(미매칭)</t>
         </is>
       </c>
     </row>
@@ -17367,7 +17359,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-08-30</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,452 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,417 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,452 (80.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,417 (80.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,078/255,452 (8.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,070/255,417 (8.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
+          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr"/>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
+          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
+          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr"/>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
+          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr"/>
@@ -6812,12 +6812,12 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
+          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr"/>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14229,7 +14229,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17359,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-02</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,417 (94.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,417 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,452 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,417 (80.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,452 (80.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,417 (71.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,070/255,417 (8.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,078/255,452 (8.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr"/>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr"/>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr"/>
@@ -6812,12 +6812,12 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr"/>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.SESSION_CNT` 비영 4,376,338/4,376,339 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 4,376,338/4,376,339 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6991,16 +6991,8 @@
           <t>DIM_GA_EVENT</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT_DIM</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+      <c r="I103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
@@ -7013,7 +7005,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7058,16 +7050,8 @@
           <t>DIM_GA_EVENT</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT_DIM</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+      <c r="I104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
@@ -7080,7 +7064,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7125,16 +7109,8 @@
           <t>DIM_GA_EVENT</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT_DIM</t>
-        </is>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+      <c r="I105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
@@ -7147,7 +7123,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_EVENT` 78,661행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7259,16 +7235,8 @@
           <t>DIM_GA_SOURCE</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE</t>
-        </is>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+      <c r="I107" s="4" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
@@ -7281,7 +7249,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7326,16 +7294,8 @@
           <t>DIM_GA_SOURCE</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE</t>
-        </is>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+      <c r="I108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr"/>
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="5" t="inlineStr">
         <is>
@@ -7344,7 +7304,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7465,12 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
+          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
@@ -7521,7 +7481,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.SCROLL_DEPTH` 비영 904,700/4,376,339 (20.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 904,700/4,376,339 (20.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7536,7 @@
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_GA_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -7621,16 +7581,8 @@
           <t>DIM_GA_SOURCE</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+      <c r="I113" s="4" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr">
         <is>
@@ -7639,7 +7591,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_GA_SOURCE` 689행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14181,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17311,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-03</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -56,17 +56,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -693,16 +693,8 @@
           <t>SV metric — 분자: DEV_CNT / 분모: GOAL_CNT</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>월 개발건 / 월 회원개발목표</t>
@@ -710,12 +702,12 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -760,16 +752,8 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: GOAL_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>누계 개발건 / 누계 회원개발목표</t>
@@ -777,12 +761,12 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -827,16 +811,8 @@
           <t>SV metric — 분자: DEV_CNT(YR) / 분모: GOAL_CNT(YR)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>연 개발건 / 연 회원개발목표</t>
@@ -844,12 +820,12 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -894,16 +870,8 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원의 CRM 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -911,12 +879,12 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,883 (5.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -961,16 +929,8 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>GA 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -978,12 +938,12 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,883 (5.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1005,12 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1072,12 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1139,12 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,487/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1206,12 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1253,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>SV metric — 분자: GA_CONV_MEMBERS / 분모: CLICKS</t>
+          <t>SV metric — 분자: AGENCY_CONV_MEMBERS / 분모: CLICKS</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1313,12 +1273,12 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.GA_CONV_MEMBERS` 비영 47,987/255,452 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1374,14 +1334,14 @@
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1441,14 +1401,14 @@
           <t>YOUTUBE, KBS, 당근 등 광고를 송출하는 플랫폼</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1464,14 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1567,14 +1527,14 @@
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1634,14 +1594,14 @@
           <t>1) 국내 2) 해외 3) 전체 4) 통합</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1701,14 +1661,14 @@
           <t>1) 사례 2) 사업 3) 굿즈 4) 통합</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1768,14 +1728,14 @@
           <t>1) 국내 사례 2) 국내 사업 3) 해외 사례 4) 해외 굿즈 5) 전체 굿즈 6) 통합</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1831,14 +1791,14 @@
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1854,14 @@
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1957,14 +1917,14 @@
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2020,14 +1980,14 @@
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2083,14 +2043,14 @@
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,167행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2108,12 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,452 (80.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2171,12 @@
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2234,12 @@
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,078/255,452 (8.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2287,7 @@
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2382,7 +2342,7 @@
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2434,25 +2394,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2497,29 +2449,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>회원이 최초가입 시 가입캠페인</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2564,29 +2508,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>회원의 최종중단일자</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2631,29 +2567,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>회원이 최종중단 시 최종캠페인</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2629,7 @@
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2756,7 +2684,7 @@
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2811,7 +2739,7 @@
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2863,16 +2791,8 @@
           <t>FME→FMM.STOP_CNT</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원중단한 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -2880,12 +2800,12 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2930,29 +2850,21 @@
           <t>FME→FMM.UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 미납인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2997,29 +2909,21 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3064,29 +2968,21 @@
           <t>FMM.DECREASE_CNT</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원사업(세부캠페인)별 총 감액 건 ( = 전체 감액금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3131,25 +3027,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3194,25 +3082,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr">
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3257,25 +3137,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3320,25 +3192,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3383,25 +3247,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3446,25 +3302,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="6" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3509,29 +3357,21 @@
           <t>SV metric — 분자: MONTH_END_ACTIVE_CNT / 분모: YEAR_START_ACTIVE_CNT + DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3576,16 +3416,8 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>누계개발 건 / 활동건</t>
@@ -3593,12 +3425,12 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,883 (5.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3643,29 +3475,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD) + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3710,25 +3534,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="6" t="inlineStr">
+      <c r="L52" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3773,16 +3589,8 @@
           <t>FMM.YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>전년도 연도말 활동회원 건수</t>
@@ -3790,12 +3598,12 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 35,527,740/40,054,883 (88.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3840,18 +3648,10 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="6" t="inlineStr">
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3903,29 +3703,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
           <t>활동, 미납1~미납5까지의 회원 포함</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr">
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3970,29 +3762,21 @@
           <t>FMM.MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
         </is>
       </c>
-      <c r="L56" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4037,25 +3821,17 @@
           <t>FMM.PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 37,695,311/40,054,883 (94.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4100,16 +3876,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>중단(건) / (개발(건) + 연도초활동회원(건))</t>
@@ -4117,12 +3885,12 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,883 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4167,16 +3935,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
           <t>중단(건) / 개발(건)</t>
@@ -4184,12 +3944,12 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,883 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4234,16 +3994,8 @@
           <t>SV metric — 분자: STOP_CNT[신규] / 분모: DEV_CNT[신규] + PREV_MONTH_END_ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>신규중단(건) / (당월 신규개발(건) + 전월말 신규활동회원건)</t>
@@ -4251,12 +4003,12 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4053,8 @@
           <t>SV metric — 분자: STOP_CNT[기존] / 분모: DEV_CNT[기존] + PREV_MONTH_END_ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
           <t>기존중단(건) / (당월 기존개발(건) + 전월말 기존활동회원건)</t>
@@ -4318,12 +4062,12 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4368,16 +4112,8 @@
           <t>SV metric — 분자: STOP_CNT(주합) / 분모: 주간 일수(DIM_DATE)</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
           <t>해당주간 총 중단건수 / 해당 주간 일수</t>
@@ -4385,12 +4121,12 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4178,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치)</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4501,7 +4237,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치) / (전주/전월/전년 수치) * 100</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4553,29 +4289,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>활동회원 건 / 활동회원 명</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4620,16 +4348,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>납입회비 원 / (활동회원 건 * 10,000)</t>
@@ -4637,12 +4357,12 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4687,16 +4407,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: ACTIVE_CUM_CNT ×10000</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>누계납입회비 원 / (누계 활동회원 건 * 10,000)</t>
@@ -4704,12 +4416,12 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4754,16 +4466,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: BILLED_AMT</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>(납입회비 원 / 청구회비 원) * 100</t>
@@ -4771,12 +4475,12 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4821,16 +4525,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: BILLED_AMT(YTD)</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>(누계납부회비 원 / 누계 청구회비 원) * 100</t>
@@ -4838,12 +4534,12 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4888,25 +4584,17 @@
           <t>FMM.REGULAR_FEE</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 35,433,287/40,054,883 (88.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4951,22 +4639,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
           <t>정기회원이 정기후원사업 외 비지정(기타, 국내사업, 해외사업)으로 납부하는 일시회비</t>
         </is>
       </c>
-      <c r="L71" s="6" t="inlineStr">
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5018,22 +4698,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
           <t>일시회원이 납부하는 회비</t>
         </is>
       </c>
-      <c r="L72" s="6" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5085,25 +4757,17 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I73" s="4" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5148,25 +4812,17 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr"/>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5211,25 +4867,17 @@
           <t>FMM.BILLED_AMT</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 37,148,524/40,054,883 (92.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5281,7 +4929,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L76" s="6" t="inlineStr">
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5340,7 +4988,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5399,7 +5047,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L78" s="6" t="inlineStr">
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5458,7 +5106,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L79" s="6" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5510,29 +5158,21 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
           <t>미납(건) / 활동(건)</t>
         </is>
       </c>
-      <c r="L80" s="7" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5577,29 +5217,21 @@
           <t>SV metric — 분자: UNPAID_CNT[신규] / 분모: ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
           <t>신규미납(건) / 신규활동(건)</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5644,29 +5276,21 @@
           <t>SV metric — 분자: UNPAID_CNT[기존] / 분모: ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
           <t>기존미납(건) / 기존활동(건)</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5711,29 +5335,21 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I83" s="4" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
           <t>후원사업 미납(건) / 후원사업 활동(건)</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5401,7 @@
           <t>(월초미납명수 − 월말미납명수) / 월초미납명수</t>
         </is>
       </c>
-      <c r="L84" s="6" t="inlineStr">
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5834,7 +5450,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>SV metric — 분자: 납입전환 회원(명) / 분모: GA 미납서비스 클릭회원(명)</t>
+          <t>SV metric — 분자: 납입전환 회원(명) / 분모: BigQuery 미납서비스 클릭회원(명)</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr"/>
@@ -5844,7 +5460,7 @@
           <t>납입회원(명) / 미납서비스 클릭회원(명) * 100</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="L85" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5896,29 +5512,21 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
           <t>CRM &gt; 회원요약정보 &gt; 회비내역 &gt; 미납/환급정보 &gt; 미납내역</t>
         </is>
       </c>
-      <c r="L86" s="6" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -5963,29 +5571,21 @@
           <t>FMM.CAMPAIGN_UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6030,22 +5630,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
           <t>회원상태별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L88" s="6" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6097,29 +5689,21 @@
           <t>FSE.SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L89" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6164,16 +5748,8 @@
           <t>FSE.SUCCESS_MEMBERS</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -6181,12 +5757,12 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6231,16 +5807,8 @@
           <t>FSE.FAIL_MEMBERS</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -6248,12 +5816,12 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.FAIL_MEMBERS` 비영 1,986,871/38,467,142 (5.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6298,29 +5866,21 @@
           <t>FSE.LETTER_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L92" s="7" t="inlineStr">
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6365,18 +5925,10 @@
           <t>FSE (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I93" s="4" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="6" t="inlineStr">
+      <c r="L93" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6428,29 +5980,21 @@
           <t>FSE.GIFT_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L94" s="7" t="inlineStr">
+      <c r="L94" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6495,25 +6039,17 @@
           <t>FSE.GIFT_PART_AMT</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.GIFT_PART_AMT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6550,26 +6086,18 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>FGA (measure — 컬럼 06_DDL.sql 확인)</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+          <t>FBQ (measure — 컬럼 06_DDL.sql 확인)</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L96" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6613,26 +6141,18 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>FGA (measure — 컬럼 06_DDL.sql 확인)</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+          <t>FBQ (measure — 컬럼 06_DDL.sql 확인)</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr"/>
+      <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="L97" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6676,26 +6196,18 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>FGA (measure — 컬럼 06_DDL.sql 확인)</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+          <t>FBQ (measure — 컬럼 06_DDL.sql 확인)</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr"/>
       <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="L98" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6739,26 +6251,18 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>FGA (measure — 컬럼 06_DDL.sql 확인)</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+          <t>FBQ (measure — 컬럼 06_DDL.sql 확인)</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr"/>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="L99" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6802,26 +6306,18 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>FGA (measure — 컬럼 06_DDL.sql 확인)</t>
-        </is>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+          <t>FBQ (measure — 컬럼 06_DDL.sql 확인)</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="L100" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6865,33 +6361,25 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>FGA.SESSION_CNT</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+          <t>FBQ.SESSION_CNT</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 4,376,338/4,376,339 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6416,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -6939,14 +6427,14 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="7" t="inlineStr">
+      <c r="L102" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6983,12 +6471,12 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
@@ -6998,7 +6486,7 @@
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="L103" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7042,12 +6530,12 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr"/>
@@ -7057,7 +6545,7 @@
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
         </is>
       </c>
-      <c r="L104" s="5" t="inlineStr">
+      <c r="L104" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7101,12 +6589,12 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr"/>
@@ -7116,7 +6604,7 @@
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L105" s="5" t="inlineStr">
+      <c r="L105" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7183,14 +6671,14 @@
           <t>2024 기념일 캠페인 / 2024 ACL 등</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="L106" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7227,12 +6715,12 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE</t>
+          <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE</t>
+          <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr"/>
@@ -7242,7 +6730,7 @@
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
         </is>
       </c>
-      <c r="L107" s="5" t="inlineStr">
+      <c r="L107" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7286,18 +6774,18 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE</t>
+          <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE</t>
+          <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr"/>
       <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="L108" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7341,18 +6829,18 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>FGA(attr)</t>
+          <t>FBQ(attr)</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>FGA(attr)</t>
+          <t>FBQ(attr)</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr"/>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="L109" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7396,12 +6884,12 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>FGA(attr)</t>
+          <t>FBQ(attr)</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>FGA(attr)</t>
+          <t>FBQ(attr)</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr"/>
@@ -7411,7 +6899,7 @@
           <t>예) https://m.goodneighbors.kr/campaign/turn25b</t>
         </is>
       </c>
-      <c r="L110" s="5" t="inlineStr">
+      <c r="L110" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7455,33 +6943,25 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>FGA.SCROLL_DEPTH</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>BIGQUERY_REFINED_DATA</t>
-        </is>
-      </c>
+          <t>FBQ.SCROLL_DEPTH</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 904,700/4,376,339 (20.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -7518,7 +6998,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>FGA</t>
+          <t>FBQ</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -7529,14 +7009,14 @@
       <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="7" t="inlineStr">
+      <c r="L112" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -7573,18 +7053,18 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE</t>
+          <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE</t>
+          <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr"/>
-      <c r="L113" s="5" t="inlineStr">
+      <c r="L113" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7636,25 +7116,17 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MEMBER_DK</t>
-        </is>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="6" t="inlineStr">
+      <c r="L114" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7699,25 +7171,17 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MEMBER_DK</t>
-        </is>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="6" t="inlineStr">
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7762,25 +7226,17 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MEMBER_DK</t>
-        </is>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I116" s="4" t="inlineStr"/>
+      <c r="J116" s="4" t="inlineStr"/>
       <c r="K116" s="4" t="inlineStr"/>
-      <c r="L116" s="5" t="inlineStr">
+      <c r="L116" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7825,29 +7281,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
           <t>신규: 당해년도 개발, 기존: 당해년도 이전 개발</t>
         </is>
       </c>
-      <c r="L117" s="6" t="inlineStr">
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7892,25 +7340,17 @@
           <t>DIM_ORG</t>
         </is>
       </c>
-      <c r="I118" s="4" t="inlineStr">
-        <is>
-          <t>CRM_ORG.DEPT_ID</t>
-        </is>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>TM_CM_DEPT_INFO</t>
-        </is>
-      </c>
+      <c r="I118" s="4" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr"/>
       <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="6" t="inlineStr">
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7955,25 +7395,17 @@
           <t>DIM_ORG</t>
         </is>
       </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t>CRM_ORG.DEPT_ID</t>
-        </is>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>TM_CM_DEPT_INFO</t>
-        </is>
-      </c>
+      <c r="I119" s="4" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="6" t="inlineStr">
+      <c r="L119" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8018,25 +7450,17 @@
           <t>DIM_ORG</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr">
-        <is>
-          <t>CRM_ORG.DEPT_ID</t>
-        </is>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>TM_CM_DEPT_INFO</t>
-        </is>
-      </c>
+      <c r="I120" s="4" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr"/>
       <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="6" t="inlineStr">
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8092,14 +7516,14 @@
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="6" t="inlineStr">
+      <c r="L121" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8155,14 +7579,14 @@
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="6" t="inlineStr">
+      <c r="L122" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8218,14 +7642,14 @@
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="6" t="inlineStr">
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8281,14 +7705,14 @@
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
-      <c r="L124" s="6" t="inlineStr">
+      <c r="L124" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8336,7 +7760,7 @@
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="6" t="inlineStr">
+      <c r="L125" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8388,22 +7812,14 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MEMBER_DK</t>
-        </is>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
           <t>"페이지 경로+쿼리 문자열"에서 파생. URL에서 childnum= 뒤에 오는 13자리. 예) https://gni.kr/url/25acl_25ABC.gn?memnum=1831636&amp;childnum=CMR-0102-002758 → 결연아동코드 = CMR-0102-002758</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="L126" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -8455,25 +7871,17 @@
           <t>DIM_SPONSORSHIP</t>
         </is>
       </c>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
-        </is>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
-        </is>
-      </c>
+      <c r="I127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr"/>
-      <c r="L127" s="6" t="inlineStr">
+      <c r="L127" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8518,29 +7926,21 @@
           <t>DIM_SPONSORSHIP</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
-        </is>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
-        </is>
-      </c>
+      <c r="I128" s="4" t="inlineStr"/>
+      <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
           <t>국내사단(국내아동권리보호사업(사단법인), 결식아동지원, 아동학대예방, 저소득가정지원), 국내사복(국내아동권리보호사업(사회복지법인), 국내사업, 좋은이웃(사복)), 결연(해외아동결연), 해외구호(희망학교지원사업, 해외교육지원사업, 보건의료지원사업, 식수위생지원사업, 재난구호지원사업, 해외지역개발지원사업), 기타(대북지원사업, 좋은이웃, 전체사업지원)</t>
         </is>
       </c>
-      <c r="L128" s="6" t="inlineStr">
+      <c r="L128" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8585,25 +7985,17 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
-        </is>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
-        </is>
-      </c>
+      <c r="I129" s="4" t="inlineStr"/>
+      <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr"/>
-      <c r="L129" s="6" t="inlineStr">
+      <c r="L129" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8648,25 +8040,17 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
-        </is>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
-        </is>
-      </c>
+      <c r="I130" s="4" t="inlineStr"/>
+      <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="6" t="inlineStr">
+      <c r="L130" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8098,7 @@
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr"/>
-      <c r="L131" s="6" t="inlineStr">
+      <c r="L131" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8769,7 +8153,7 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="6" t="inlineStr">
+      <c r="L132" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8824,7 +8208,7 @@
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr"/>
-      <c r="L133" s="6" t="inlineStr">
+      <c r="L133" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8876,25 +8260,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I134" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="6" t="inlineStr">
+      <c r="L134" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8939,25 +8315,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I135" s="4" t="inlineStr"/>
+      <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="6" t="inlineStr">
+      <c r="L135" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9002,25 +8370,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I136" s="4" t="inlineStr"/>
+      <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="6" t="inlineStr">
+      <c r="L136" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 7,925,716행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9065,25 +8425,17 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr"/>
-      <c r="L137" s="6" t="inlineStr">
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9128,25 +8480,17 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I138" s="4" t="inlineStr"/>
+      <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr"/>
-      <c r="L138" s="6" t="inlineStr">
+      <c r="L138" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9191,25 +8535,17 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I139" s="4" t="inlineStr"/>
+      <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="6" t="inlineStr">
+      <c r="L139" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9257,7 +8593,7 @@
       <c r="I140" s="4" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr"/>
-      <c r="L140" s="6" t="inlineStr">
+      <c r="L140" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9312,14 +8648,14 @@
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="6" t="inlineStr">
+      <c r="L141" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_DATE` 16,437행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9367,7 +8703,7 @@
       <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr"/>
-      <c r="L142" s="6" t="inlineStr">
+      <c r="L142" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9422,7 +8758,7 @@
       <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr"/>
-      <c r="L143" s="6" t="inlineStr">
+      <c r="L143" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9477,7 +8813,7 @@
       <c r="I144" s="4" t="inlineStr"/>
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr"/>
-      <c r="L144" s="6" t="inlineStr">
+      <c r="L144" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9532,7 +8868,7 @@
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="6" t="inlineStr">
+      <c r="L145" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9587,7 +8923,7 @@
       <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="6" t="inlineStr">
+      <c r="L146" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9642,7 +8978,7 @@
       <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr"/>
-      <c r="L147" s="6" t="inlineStr">
+      <c r="L147" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9697,7 +9033,7 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="6" t="inlineStr">
+      <c r="L148" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9752,7 +9088,7 @@
       <c r="I149" s="4" t="inlineStr"/>
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr"/>
-      <c r="L149" s="6" t="inlineStr">
+      <c r="L149" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9807,7 +9143,7 @@
       <c r="I150" s="4" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="6" t="inlineStr">
+      <c r="L150" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9870,14 +9206,14 @@
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
-      <c r="L151" s="6" t="inlineStr">
+      <c r="L151" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9922,25 +9258,17 @@
           <t>FME→FMM.DEV_MEMBERS</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I152" s="4" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -9985,25 +9313,17 @@
           <t>FME→FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I153" s="4" t="inlineStr"/>
+      <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr"/>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10048,25 +9368,17 @@
           <t>FME→FMM.INCREASE_MEMBERS</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I154" s="4" t="inlineStr"/>
+      <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="7" t="inlineStr">
+      <c r="L154" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10111,25 +9423,17 @@
           <t>FME→FMM.INCREASE_CNT</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I155" s="4" t="inlineStr"/>
+      <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr"/>
-      <c r="L155" s="7" t="inlineStr">
+      <c r="L155" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10174,14 +9478,10 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
-        </is>
-      </c>
+      <c r="I156" s="4" t="inlineStr"/>
       <c r="J156" s="4" t="inlineStr"/>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="7" t="inlineStr">
+      <c r="L156" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10233,14 +9533,10 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
-        </is>
-      </c>
+      <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="7" t="inlineStr">
+      <c r="L157" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10292,14 +9588,10 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
-        </is>
-      </c>
+      <c r="I158" s="4" t="inlineStr"/>
       <c r="J158" s="4" t="inlineStr"/>
       <c r="K158" s="4" t="inlineStr"/>
-      <c r="L158" s="7" t="inlineStr">
+      <c r="L158" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10351,14 +9643,10 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I159" s="4" t="inlineStr">
-        <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
-        </is>
-      </c>
+      <c r="I159" s="4" t="inlineStr"/>
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr"/>
-      <c r="L159" s="7" t="inlineStr">
+      <c r="L159" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10410,25 +9698,17 @@
           <t>FMM.ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I160" s="4" t="inlineStr"/>
+      <c r="J160" s="4" t="inlineStr"/>
       <c r="K160" s="4" t="inlineStr"/>
-      <c r="L160" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 38,423,125/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10473,25 +9753,17 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10536,18 +9808,10 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I162" s="4" t="inlineStr"/>
+      <c r="J162" s="4" t="inlineStr"/>
       <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="6" t="inlineStr">
+      <c r="L162" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10599,25 +9863,17 @@
           <t>FMM.ACTIVE_CUM_CNT</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I163" s="4" t="inlineStr"/>
+      <c r="J163" s="4" t="inlineStr"/>
       <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="7" t="inlineStr">
+      <c r="L163" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10662,18 +9918,10 @@
           <t>FSE (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
-        </is>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I164" s="4" t="inlineStr"/>
+      <c r="J164" s="4" t="inlineStr"/>
       <c r="K164" s="4" t="inlineStr"/>
-      <c r="L164" s="6" t="inlineStr">
+      <c r="L164" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10725,18 +9973,10 @@
           <t>FSE (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I165" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
-        </is>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I165" s="4" t="inlineStr"/>
+      <c r="J165" s="4" t="inlineStr"/>
       <c r="K165" s="4" t="inlineStr"/>
-      <c r="L165" s="6" t="inlineStr">
+      <c r="L165" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10788,25 +10028,17 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
-        </is>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+      <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr"/>
       <c r="K166" s="4" t="inlineStr"/>
-      <c r="L166" s="6" t="inlineStr">
+      <c r="L166" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -10851,22 +10083,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I167" s="4" t="inlineStr"/>
+      <c r="J167" s="4" t="inlineStr"/>
       <c r="K167" s="4" t="inlineStr">
         <is>
           <t>캠페인 가입 이후 납입하는 회비</t>
         </is>
       </c>
-      <c r="L167" s="6" t="inlineStr">
+      <c r="L167" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10925,7 +10149,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 개월수</t>
         </is>
       </c>
-      <c r="L168" s="6" t="inlineStr">
+      <c r="L168" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10984,7 +10208,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 년수</t>
         </is>
       </c>
-      <c r="L169" s="6" t="inlineStr">
+      <c r="L169" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11036,16 +10260,8 @@
           <t>SV metric — 분자: Σ(유지기간×DEV_MEMBERS) / 분모: DEV_MEMBERS(총)</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I170" s="4" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr"/>
       <c r="K170" s="4" t="inlineStr">
         <is>
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
@@ -11053,12 +10269,12 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11110,7 +10326,7 @@
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
         </is>
       </c>
-      <c r="L171" s="6" t="inlineStr">
+      <c r="L171" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11169,7 +10385,7 @@
           <t>N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수</t>
         </is>
       </c>
-      <c r="L172" s="6" t="inlineStr">
+      <c r="L172" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11228,7 +10444,7 @@
           <t>(N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수) × 100</t>
         </is>
       </c>
-      <c r="L173" s="6" t="inlineStr">
+      <c r="L173" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11287,7 +10503,7 @@
           <t>평균 납입회비 × 평균 활동 기간</t>
         </is>
       </c>
-      <c r="L174" s="6" t="inlineStr">
+      <c r="L174" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11346,7 +10562,7 @@
           <t>광고비(편성비) 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L175" s="5" t="inlineStr">
+      <c r="L175" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11398,29 +10614,21 @@
           <t>SV metric — 분자: FUNDRAISING_COST / 분모: DEV_CNT[신규]</t>
         </is>
       </c>
-      <c r="I176" s="4" t="inlineStr">
-        <is>
-          <t>ERP_BUDGET.EXEC_AMT</t>
-        </is>
-      </c>
-      <c r="J176" s="4" t="inlineStr">
-        <is>
-          <t>BDGT_ACMSLT_LEDGER</t>
-        </is>
-      </c>
+      <c r="I176" s="4" t="inlineStr"/>
+      <c r="J176" s="4" t="inlineStr"/>
       <c r="K176" s="4" t="inlineStr">
         <is>
           <t>ERP 모금성 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L176" s="7" t="inlineStr">
+      <c r="L176" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BUDGET.FUNDRAISING_COST` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BUDGET` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11465,16 +10673,8 @@
           <t>SV metric — 분자: PAID_FEE(또는 LTV) − 비용 / 분모: 비용(FBD)</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J177" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I177" s="4" t="inlineStr"/>
+      <c r="J177" s="4" t="inlineStr"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
           <t>(총 수익−총 비용) / 총 비용 × 100</t>
@@ -11482,12 +10682,12 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11532,29 +10732,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I178" s="4" t="inlineStr"/>
+      <c r="J178" s="4" t="inlineStr"/>
       <c r="K178" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
         </is>
       </c>
-      <c r="L178" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L178" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11599,29 +10791,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J179" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I179" s="4" t="inlineStr"/>
+      <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
         </is>
       </c>
-      <c r="L179" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11666,29 +10850,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J180" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I180" s="4" t="inlineStr"/>
+      <c r="J180" s="4" t="inlineStr"/>
       <c r="K180" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
         </is>
       </c>
-      <c r="L180" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,116/40,054,883 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11733,16 +10909,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I181" s="4" t="inlineStr"/>
+      <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
           <t>캠페인별 중단(건) / (캠페인별 개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -11750,12 +10918,12 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,883 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11800,16 +10968,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I182" s="4" t="inlineStr"/>
+      <c r="J182" s="4" t="inlineStr"/>
       <c r="K182" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 중단(건) / (캠페인 개발(건) + 캠페인 전월말활동회원(건))</t>
@@ -11817,12 +10977,12 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,883 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11867,16 +11027,8 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I183" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J183" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I183" s="4" t="inlineStr"/>
+      <c r="J183" s="4" t="inlineStr"/>
       <c r="K183" s="4" t="inlineStr">
         <is>
           <t>캠페인별 누계중단(건) / (캠페인별 누계개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -11884,12 +11036,12 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,883 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11934,16 +11086,8 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J184" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I184" s="4" t="inlineStr"/>
+      <c r="J184" s="4" t="inlineStr"/>
       <c r="K184" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 누계중단(건) / 캠페인별 누계개발(건)</t>
@@ -11951,12 +11095,12 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,883 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12001,16 +11145,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I185" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J185" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I185" s="4" t="inlineStr"/>
+      <c r="J185" s="4" t="inlineStr"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 중단(건) / (캠페인별 납입방식 개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -12018,12 +11154,12 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,883 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12068,29 +11204,21 @@
           <t>FMM.CHURN_CNT</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J186" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr"/>
       <c r="K186" s="4" t="inlineStr">
         <is>
           <t>후원취소 및 감액한 후원사업의 금액 / 10,000</t>
         </is>
       </c>
-      <c r="L186" s="7" t="inlineStr">
+      <c r="L186" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12135,29 +11263,21 @@
           <t>SV metric — 분자: CHURN_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I187" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J187" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I187" s="4" t="inlineStr"/>
+      <c r="J187" s="4" t="inlineStr"/>
       <c r="K187" s="4" t="inlineStr">
         <is>
           <t>캠페인별 이탈(건) / 캠페인별 개발(건)</t>
         </is>
       </c>
-      <c r="L187" s="7" t="inlineStr">
+      <c r="L187" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12202,16 +11322,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I188" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J188" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I188" s="4" t="inlineStr"/>
+      <c r="J188" s="4" t="inlineStr"/>
       <c r="K188" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12219,12 +11331,12 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12269,16 +11381,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J189" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I189" s="4" t="inlineStr"/>
+      <c r="J189" s="4" t="inlineStr"/>
       <c r="K189" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12286,12 +11390,12 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12336,16 +11440,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J190" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I190" s="4" t="inlineStr"/>
+      <c r="J190" s="4" t="inlineStr"/>
       <c r="K190" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12353,12 +11449,12 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12403,16 +11499,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I191" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J191" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I191" s="4" t="inlineStr"/>
+      <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12420,12 +11508,12 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12470,16 +11558,8 @@
           <t>SV metric — 분자: PAID_FEE(캠페인) / 분모: PAID_FEE(전체)</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J192" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I192" s="4" t="inlineStr"/>
+      <c r="J192" s="4" t="inlineStr"/>
       <c r="K192" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입회비 / 총 납입회비 금액 × 100</t>
@@ -12487,12 +11567,12 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,538/40,054,883 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12537,29 +11617,21 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J193" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I193" s="4" t="inlineStr"/>
+      <c r="J193" s="4" t="inlineStr"/>
       <c r="K193" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L193" s="7" t="inlineStr">
+      <c r="L193" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12604,29 +11676,21 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I194" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J194" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I194" s="4" t="inlineStr"/>
+      <c r="J194" s="4" t="inlineStr"/>
       <c r="K194" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L194" s="7" t="inlineStr">
+      <c r="L194" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12671,29 +11735,21 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT(캠페인) / 분모: CAMPAIGN_UNPAID_CNT(전체)</t>
         </is>
       </c>
-      <c r="I195" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J195" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I195" s="4" t="inlineStr"/>
+      <c r="J195" s="4" t="inlineStr"/>
       <c r="K195" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비 / 총 미납회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L195" s="7" t="inlineStr">
+      <c r="L195" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12738,29 +11794,21 @@
           <t>SV metric — 분자: SEND_MEMBERS / 분모: 전체회원수(명)</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J196" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I196" s="4" t="inlineStr"/>
+      <c r="J196" s="4" t="inlineStr"/>
       <c r="K196" s="4" t="inlineStr">
         <is>
           <t>서비스별 발송수(명) / 전체회원수(명) × 100</t>
         </is>
       </c>
-      <c r="L196" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L196" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12805,16 +11853,8 @@
           <t>SV metric — 분자: SUCCESS_MEMBERS / 분모: SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
-        </is>
-      </c>
-      <c r="J197" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I197" s="4" t="inlineStr"/>
+      <c r="J197" s="4" t="inlineStr"/>
       <c r="K197" s="4" t="inlineStr">
         <is>
           <t>발송성공수(명) / 발송수(명) × 100</t>
@@ -12822,12 +11862,12 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12869,7 +11909,7 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>SV metric — 분자: GA 클릭회원(명, distinct) / 분모: SEND_MEMBERS</t>
+          <t>SV metric — 분자: BigQuery 클릭회원(명, distinct) / 분모: SEND_MEMBERS</t>
         </is>
       </c>
       <c r="I198" s="4" t="inlineStr"/>
@@ -12879,7 +11919,7 @@
           <t>클릭수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L198" s="5" t="inlineStr">
+      <c r="L198" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -12928,19 +11968,11 @@
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>SV metric — 분자: DEV_MEMBERS / 분모: GA 클릭회원(명)</t>
-        </is>
-      </c>
-      <c r="I199" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J199" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+          <t>SV metric — 분자: DEV_MEMBERS / 분모: BigQuery 클릭회원(명)</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr"/>
+      <c r="J199" s="4" t="inlineStr"/>
       <c r="K199" s="4" t="inlineStr">
         <is>
           <t>개발회원(명) / 서비스 클릭수(명) × 100</t>
@@ -12948,12 +11980,12 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -13005,7 +12037,7 @@
           <t>(증액 회원수(명,건) / 서비스별 발송 성공회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L200" s="6" t="inlineStr">
+      <c r="L200" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13064,7 +12096,7 @@
           <t>(서비스별 증액 후 N개월 시점 유지 회원(명,건) / 서비스별 증액 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L201" s="6" t="inlineStr">
+      <c r="L201" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13123,7 +12155,7 @@
           <t>(서비스별 발송 후 N개월 시점 유지 회원(명,건) / 서비스별 참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L202" s="6" t="inlineStr">
+      <c r="L202" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13182,7 +12214,7 @@
           <t>(서비스별 증액회원 중 납입회원(명,건) / 서비스별 증액회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 증액회원의 납입회비) / 서비스별 증액회원(명)</t>
         </is>
       </c>
-      <c r="L203" s="6" t="inlineStr">
+      <c r="L203" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13241,7 +12273,7 @@
           <t>(서비스별 참여회원 중 납입회원(명,건) / 서비스별 참여회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 참여회원의 납입회비) / 서비스별 참여회원(명)</t>
         </is>
       </c>
-      <c r="L204" s="6" t="inlineStr">
+      <c r="L204" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13300,7 +12332,7 @@
           <t>(서비스별 증액회원 중 중단회원(명,건) / 서비스별 증액회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L205" s="6" t="inlineStr">
+      <c r="L205" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13359,7 +12391,7 @@
           <t>(서비스별 참여회원 중 중단회원(명,건) / 서비스별 참여회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L206" s="6" t="inlineStr">
+      <c r="L206" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13418,7 +12450,7 @@
           <t>(해당 캠페인 서비스별 증액회원(명,건) / 서비스별 전체 증액회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L207" s="6" t="inlineStr">
+      <c r="L207" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13477,7 +12509,7 @@
           <t>(해당 캠페인 서비스별 참여회원(명,건) / 서비스별 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L208" s="6" t="inlineStr">
+      <c r="L208" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13536,7 +12568,7 @@
           <t>(해당 서비스·캠페인 조합에서 N개월 시점 유지 회원(명,건) / 해당 캠페인 가입회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L209" s="6" t="inlineStr">
+      <c r="L209" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13588,29 +12620,21 @@
           <t>SV metric — 분자: LETTER_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I210" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
-        </is>
-      </c>
-      <c r="J210" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I210" s="4" t="inlineStr"/>
+      <c r="J210" s="4" t="inlineStr"/>
       <c r="K210" s="4" t="inlineStr">
         <is>
           <t>(서비스별 서신 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L210" s="7" t="inlineStr">
+      <c r="L210" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -13662,7 +12686,7 @@
           <t>(서신참여 후 N개월 시점 유지 회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L211" s="6" t="inlineStr">
+      <c r="L211" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13721,7 +12745,7 @@
           <t>(서비스별 서신참여회원 중 납입회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 서신참여회원의 납입회비) / 서비스별 서신참여회원(명)</t>
         </is>
       </c>
-      <c r="L212" s="6" t="inlineStr">
+      <c r="L212" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13780,7 +12804,7 @@
           <t>(서비스별 서신참여회원 중 중단회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L213" s="6" t="inlineStr">
+      <c r="L213" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13839,7 +12863,7 @@
           <t>(해당 캠페인 서비스별 서신참여회원(명,건) / 서비스별 전체 서신참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L214" s="6" t="inlineStr">
+      <c r="L214" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13891,29 +12915,21 @@
           <t>SV metric — 분자: GIFT_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I215" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
-        </is>
-      </c>
-      <c r="J215" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I215" s="4" t="inlineStr"/>
+      <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
           <t>(서비스별 선물금 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L215" s="7" t="inlineStr">
+      <c r="L215" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -13965,7 +12981,7 @@
           <t>(서비스별 선물금참여 후 N개월 시점 유지 회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L216" s="6" t="inlineStr">
+      <c r="L216" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14024,7 +13040,7 @@
           <t>(서비스별 선물금참여회원 중 납입회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 선물금참여회원의 납입회비) / 서비스별 선물금참여회원수(명)</t>
         </is>
       </c>
-      <c r="L217" s="6" t="inlineStr">
+      <c r="L217" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14083,7 +13099,7 @@
           <t>(서비스별 선물금참여회원 중 중단회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L218" s="6" t="inlineStr">
+      <c r="L218" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14142,7 +13158,7 @@
           <t>(해당 캠페인 서비스별 선물금참여회원(명,건) / 서비스별 전체 선물금참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L219" s="6" t="inlineStr">
+      <c r="L219" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -16130,20 +15146,16 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>(215밖)</t>
-        </is>
-      </c>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>FACT_AD_PERFORMANCE.GA_CONV_MEMBERS</t>
+          <t>(미매칭 — GOLD 물리·SV 대응 미확인)</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>(미매칭)</t>
         </is>
       </c>
     </row>
@@ -16173,20 +15185,16 @@
           <t>숫자(회계)</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>(215밖)</t>
-        </is>
-      </c>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>FACT_AD_PERFORMANCE.GA_CONV_MEMBERS</t>
+          <t>(미매칭 — GOLD 물리·SV 대응 미확인)</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리(단위)</t>
+          <t>(미매칭)</t>
         </is>
       </c>
     </row>
@@ -18110,7 +17118,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -18153,7 +17161,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -18282,7 +17290,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -18329,7 +17337,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -18376,7 +17384,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -18423,7 +17431,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -18470,7 +17478,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -18517,7 +17525,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -19381,7 +18389,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -19424,7 +18432,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -20898,7 +19906,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -20941,7 +19949,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -20984,7 +19992,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -21027,7 +20035,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -21070,7 +20078,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.EVENT_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.EVENT_CNT</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -27465,7 +26473,7 @@
       </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VIEW_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VIEW_CNT</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -27508,7 +26516,7 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.EVENT_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.EVENT_CNT</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -27551,7 +26559,7 @@
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -27594,13 +26602,13 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_SESSION_DURATION</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
       <c r="I242" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -28680,7 +27688,7 @@
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -28723,7 +27731,7 @@
       </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -28766,7 +27774,7 @@
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -28809,7 +27817,7 @@
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -28852,7 +27860,7 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VIEW_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VIEW_CNT</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -28895,7 +27903,7 @@
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.EVENT_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.EVENT_CNT</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -28938,7 +27946,7 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ENGAGED_SESSIONS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ENGAGED_SESSIONS</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -28981,13 +27989,13 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.BOUNCE_RATE</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
       <c r="I275" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -29024,7 +28032,7 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ENGAGEMENT_RATE</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ENGAGEMENT_RATE</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -29067,13 +28075,13 @@
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_SESSION_DURATION</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
       <c r="I277" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -29110,7 +28118,7 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_ENGAGEMENT_TIME_PER_SESSION</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.AVG_ENGAGEMENT_TIME_PER_SESSION</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -29153,13 +28161,13 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_SESSION_DURATION</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
       <c r="I279" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리~</t>
+          <t>지표사전~</t>
         </is>
       </c>
     </row>
@@ -29196,7 +28204,7 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_ENGAGEMENT_TIME_PER_SESSION</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.AVG_ENGAGEMENT_TIME_PER_SESSION</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -29239,7 +28247,7 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VISITS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VISITS</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -29282,7 +28290,7 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.CAMPAIGN_SK</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -29325,7 +28333,7 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.UTM_CONTENT</t>
+          <t>DIM_BIGQUERY_SOURCE.UTM_CONTENT</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -29368,7 +28376,7 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.UTM_TERM</t>
+          <t>DIM_BIGQUERY_SOURCE.UTM_TERM</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -29411,7 +28419,7 @@
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
-          <t>FGA(attr)</t>
+          <t>FBQ(attr)</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -29454,7 +28462,7 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.PAGE_LOCATION</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.PAGE_LOCATION</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -30364,7 +29372,7 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -30407,13 +29415,13 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_SESSION_DURATION</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -30450,13 +29458,13 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.BOUNCE_RATE</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -30493,7 +29501,7 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SCROLL_DEPTH</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -30536,7 +29544,7 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -30579,7 +29587,7 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -30622,7 +29630,7 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -31208,7 +30216,7 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.CAMPAIGN_SK</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -31251,7 +30259,7 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.UTM_CONTENT</t>
+          <t>DIM_BIGQUERY_SOURCE.UTM_CONTENT</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -31294,7 +30302,7 @@
       </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VIEW_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VIEW_CNT</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -31337,7 +30345,7 @@
       </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32740,7 +31748,7 @@
       </c>
       <c r="G364" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -32783,13 +31791,13 @@
       </c>
       <c r="G365" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.BOUNCE_RATE</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
       <c r="I365" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -32826,13 +31834,13 @@
       </c>
       <c r="G366" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_SESSION_DURATION</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
       <c r="I366" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -32869,7 +31877,7 @@
       </c>
       <c r="G367" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.CAMPAIGN_SK</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -32912,7 +31920,7 @@
       </c>
       <c r="G368" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.UTM_CONTENT</t>
+          <t>DIM_BIGQUERY_SOURCE.UTM_CONTENT</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -32955,7 +31963,7 @@
       </c>
       <c r="G369" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.UTM_TERM</t>
+          <t>DIM_BIGQUERY_SOURCE.UTM_TERM</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -32998,7 +32006,7 @@
       </c>
       <c r="G370" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.PAGE_PATH</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.PAGE_PATH</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -33041,7 +32049,7 @@
       </c>
       <c r="G371" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.PAGE_LOCATION</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.PAGE_LOCATION</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -33084,7 +32092,7 @@
       </c>
       <c r="G372" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -33127,7 +32135,7 @@
       </c>
       <c r="G373" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -33170,7 +32178,7 @@
       </c>
       <c r="G374" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34362,7 +33370,7 @@
       </c>
       <c r="G402" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.VIEW_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.VIEW_CNT</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -34405,7 +33413,7 @@
       </c>
       <c r="G403" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -34448,7 +33456,7 @@
       </c>
       <c r="G404" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ENGAGED_SESSIONS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ENGAGED_SESSIONS</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -34491,13 +33499,13 @@
       </c>
       <c r="G405" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.BOUNCE_RATE</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
       <c r="I405" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -34534,13 +33542,13 @@
       </c>
       <c r="G406" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.AVG_SESSION_DURATION</t>
+          <t xml:space="preserve">FGA 물리적재(비가산) — </t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
       <c r="I406" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>지표사전</t>
         </is>
       </c>
     </row>
@@ -34577,7 +33585,7 @@
       </c>
       <c r="G407" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.CAMPAIGN_SK</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -34620,7 +33628,7 @@
       </c>
       <c r="G408" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.UTM_CONTENT</t>
+          <t>DIM_BIGQUERY_SOURCE.UTM_CONTENT</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -34663,7 +33671,7 @@
       </c>
       <c r="G409" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.UTM_TERM</t>
+          <t>DIM_BIGQUERY_SOURCE.UTM_TERM</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -34706,7 +33714,7 @@
       </c>
       <c r="G410" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_SOURCE.SOURCE_MEDIUM</t>
+          <t>DIM_BIGQUERY_SOURCE.SOURCE_MEDIUM</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -34749,7 +33757,7 @@
       </c>
       <c r="G411" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.PAGE_PATH</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.PAGE_PATH</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -34792,7 +33800,7 @@
       </c>
       <c r="G412" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.PAGE_LOCATION</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.PAGE_LOCATION</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -34835,7 +33843,7 @@
       </c>
       <c r="G413" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -34878,7 +33886,7 @@
       </c>
       <c r="G414" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -34921,7 +33929,7 @@
       </c>
       <c r="G415" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -34964,7 +33972,7 @@
       </c>
       <c r="G416" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.EVENT_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.EVENT_CNT</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -35007,7 +34015,7 @@
       </c>
       <c r="G417" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.ACTIVE_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.ACTIVE_USERS</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -35050,7 +34058,7 @@
       </c>
       <c r="G418" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.TOTAL_USERS</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.TOTAL_USERS</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -35429,7 +34437,7 @@
       </c>
       <c r="G427" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -35472,7 +34480,7 @@
       </c>
       <c r="G428" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -35515,7 +34523,7 @@
       </c>
       <c r="G429" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -35558,7 +34566,7 @@
       </c>
       <c r="G430" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -35601,7 +34609,7 @@
       </c>
       <c r="G431" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.EVENT_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.EVENT_CNT</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -35722,7 +34730,7 @@
       </c>
       <c r="G434" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -35765,7 +34773,7 @@
       </c>
       <c r="G435" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -35808,7 +34816,7 @@
       </c>
       <c r="G436" s="4" t="inlineStr">
         <is>
-          <t>DIM_GA_EVENT</t>
+          <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -35851,7 +34859,7 @@
       </c>
       <c r="G437" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.SESSION_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.SESSION_CNT</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -35894,7 +34902,7 @@
       </c>
       <c r="G438" s="4" t="inlineStr">
         <is>
-          <t>FACT_GA_BEHAVIOR.EVENT_CNT</t>
+          <t>FACT_BIGQUERY_BEHAVIOR.EVENT_CNT</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -56,17 +56,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -693,8 +693,16 @@
           <t>SV metric — 분자: DEV_CNT / 분모: GOAL_CNT</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>월 개발건 / 월 회원개발목표</t>
@@ -702,12 +710,12 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -752,8 +760,16 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: GOAL_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>누계 개발건 / 누계 회원개발목표</t>
@@ -761,12 +777,12 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -811,8 +827,16 @@
           <t>SV metric — 분자: DEV_CNT(YR) / 분모: GOAL_CNT(YR)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>연 개발건 / 연 회원개발목표</t>
@@ -820,12 +844,12 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -870,8 +894,16 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원의 CRM 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -879,12 +911,12 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,884 (5.0%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -929,8 +961,16 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>GA 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -938,12 +978,12 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,884 (5.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1045,12 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,488/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1112,12 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,488/255,452 (94.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1179,12 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,488/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1246,12 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1313,12 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 47,987/255,452 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1334,14 +1374,14 @@
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1401,14 +1441,14 @@
           <t>YOUTUBE, KBS, 당근 등 광고를 송출하는 플랫폼</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1464,14 +1504,14 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1527,14 +1567,14 @@
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1594,14 +1634,14 @@
           <t>1) 국내 2) 해외 3) 전체 4) 통합</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1661,14 +1701,14 @@
           <t>1) 사례 2) 사업 3) 굿즈 4) 통합</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1728,14 +1768,14 @@
           <t>1) 국내 사례 2) 국내 사업 3) 해외 사례 4) 해외 굿즈 5) 전체 굿즈 6) 통합</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1791,14 +1831,14 @@
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1854,14 +1894,14 @@
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1917,14 +1957,14 @@
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1980,14 +2020,14 @@
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2043,14 +2083,14 @@
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2148,12 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,452 (80.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2211,12 @@
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2274,12 @@
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,081/255,452 (8.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2327,7 @@
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2342,7 +2382,7 @@
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2394,17 +2434,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2449,21 +2497,29 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>회원이 최초가입 시 가입캠페인</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2508,21 +2564,29 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>회원의 최종중단일자</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2567,21 +2631,29 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>회원이 최종중단 시 최종캠페인</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2701,7 @@
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2684,7 +2756,7 @@
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2739,7 +2811,7 @@
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2791,8 +2863,16 @@
           <t>FME→FMM.STOP_CNT</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원중단한 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -2800,12 +2880,12 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2850,21 +2930,29 @@
           <t>FME→FMM.UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 미납인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -2909,21 +2997,29 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -2968,21 +3064,29 @@
           <t>FMM.DECREASE_CNT</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원사업(세부캠페인)별 총 감액 건 ( = 전체 감액금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -3027,17 +3131,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3082,17 +3194,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3137,17 +3257,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3192,17 +3320,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3247,17 +3383,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3302,17 +3446,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr"/>
-      <c r="J48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="L48" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3357,21 +3509,29 @@
           <t>SV metric — 분자: MONTH_END_ACTIVE_CNT / 분모: YEAR_START_ACTIVE_CNT + DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
-      <c r="J49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3416,8 +3576,16 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>누계개발 건 / 활동건</t>
@@ -3425,12 +3593,12 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,884 (5.0%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3475,21 +3643,29 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD) + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3534,17 +3710,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="L52" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3589,8 +3773,16 @@
           <t>FMM.YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>전년도 연도말 활동회원 건수</t>
@@ -3598,12 +3790,12 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 35,527,741/40,054,884 (88.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3648,10 +3840,18 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="L54" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3703,21 +3903,29 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
           <t>활동, 미납1~미납5까지의 회원 포함</t>
         </is>
       </c>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="L55" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3762,21 +3970,29 @@
           <t>FMM.MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -3821,17 +4037,25 @@
           <t>FMM.PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 37,695,312/40,054,884 (94.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3876,8 +4100,16 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>중단(건) / (개발(건) + 연도초활동회원(건))</t>
@@ -3885,12 +4117,12 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3935,8 +4167,16 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
           <t>중단(건) / 개발(건)</t>
@@ -3944,12 +4184,12 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3994,8 +4234,16 @@
           <t>SV metric — 분자: STOP_CNT[신규] / 분모: DEV_CNT[신규] + PREV_MONTH_END_ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>신규중단(건) / (당월 신규개발(건) + 전월말 신규활동회원건)</t>
@@ -4003,12 +4251,12 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4053,8 +4301,16 @@
           <t>SV metric — 분자: STOP_CNT[기존] / 분모: DEV_CNT[기존] + PREV_MONTH_END_ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
           <t>기존중단(건) / (당월 기존개발(건) + 전월말 기존활동회원건)</t>
@@ -4062,12 +4318,12 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4112,8 +4368,16 @@
           <t>SV metric — 분자: STOP_CNT(주합) / 분모: 주간 일수(DIM_DATE)</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
           <t>해당주간 총 중단건수 / 해당 주간 일수</t>
@@ -4121,12 +4385,12 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4442,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치)</t>
         </is>
       </c>
-      <c r="L63" s="7" t="inlineStr">
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4237,7 +4501,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치) / (전주/전월/전년 수치) * 100</t>
         </is>
       </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="L64" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4289,21 +4553,29 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>활동회원 건 / 활동회원 명</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4348,8 +4620,16 @@
           <t>SV metric — 분자: PAID_FEE / 분모: ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>납입회비 원 / (활동회원 건 * 10,000)</t>
@@ -4357,12 +4637,12 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4407,8 +4687,16 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: ACTIVE_CUM_CNT ×10000</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>누계납입회비 원 / (누계 활동회원 건 * 10,000)</t>
@@ -4416,12 +4704,12 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4466,8 +4754,16 @@
           <t>SV metric — 분자: PAID_FEE / 분모: BILLED_AMT</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>(납입회비 원 / 청구회비 원) * 100</t>
@@ -4475,12 +4771,12 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4525,8 +4821,16 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: BILLED_AMT(YTD)</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>(누계납부회비 원 / 누계 청구회비 원) * 100</t>
@@ -4534,12 +4838,12 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4584,17 +4888,25 @@
           <t>FMM.REGULAR_FEE</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 35,433,288/40,054,884 (88.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4639,14 +4951,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
           <t>정기회원이 정기후원사업 외 비지정(기타, 국내사업, 해외사업)으로 납부하는 일시회비</t>
         </is>
       </c>
-      <c r="L71" s="7" t="inlineStr">
+      <c r="L71" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4698,14 +5018,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr"/>
-      <c r="J72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
           <t>일시회원이 납부하는 회비</t>
         </is>
       </c>
-      <c r="L72" s="7" t="inlineStr">
+      <c r="L72" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4757,17 +5085,25 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr"/>
-      <c r="J73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4812,17 +5148,25 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4867,17 +5211,25 @@
           <t>FMM.BILLED_AMT</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 37,148,525/40,054,884 (92.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4929,7 +5281,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4988,7 +5340,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="L77" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5047,7 +5399,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L78" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5106,7 +5458,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="L79" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5158,21 +5510,29 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
           <t>미납(건) / 활동(건)</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5217,21 +5577,29 @@
           <t>SV metric — 분자: UNPAID_CNT[신규] / 분모: ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
           <t>신규미납(건) / 신규활동(건)</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5276,21 +5644,29 @@
           <t>SV metric — 분자: UNPAID_CNT[기존] / 분모: ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
           <t>기존미납(건) / 기존활동(건)</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5335,21 +5711,29 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
           <t>후원사업 미납(건) / 후원사업 활동(건)</t>
         </is>
       </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5785,7 @@
           <t>(월초미납명수 − 월말미납명수) / 월초미납명수</t>
         </is>
       </c>
-      <c r="L84" s="7" t="inlineStr">
+      <c r="L84" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5460,7 +5844,7 @@
           <t>납입회원(명) / 미납서비스 클릭회원(명) * 100</t>
         </is>
       </c>
-      <c r="L85" s="6" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5512,21 +5896,29 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_ID</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
           <t>CRM &gt; 회원요약정보 &gt; 회비내역 &gt; 미납/환급정보 &gt; 미납내역</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="L86" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -5571,21 +5963,29 @@
           <t>FMM.CAMPAIGN_UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5630,14 +6030,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
           <t>회원상태별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L88" s="7" t="inlineStr">
+      <c r="L88" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5689,21 +6097,29 @@
           <t>FSE.SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr"/>
-      <c r="J89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -5748,8 +6164,16 @@
           <t>FSE.SUCCESS_MEMBERS</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr"/>
-      <c r="J90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -5757,12 +6181,12 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5807,8 +6231,16 @@
           <t>FSE.FAIL_MEMBERS</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -5816,12 +6248,12 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 1,986,871/38,467,142 (5.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5866,21 +6298,29 @@
           <t>FSE.LETTER_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5928,7 +6368,7 @@
       <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="7" t="inlineStr">
+      <c r="L93" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5980,21 +6420,29 @@
           <t>FSE.GIFT_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6039,17 +6487,25 @@
           <t>FSE.GIFT_PART_AMT</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_AMT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6553,7 @@
       <c r="I96" s="4" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="6" t="inlineStr">
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6152,7 +6608,7 @@
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="6" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6207,7 +6663,7 @@
       <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr"/>
       <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="6" t="inlineStr">
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6262,7 +6718,7 @@
       <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr"/>
-      <c r="L99" s="6" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6317,7 +6773,7 @@
       <c r="I100" s="4" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="6" t="inlineStr">
+      <c r="L100" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6369,17 +6825,25 @@
           <t>FBQ.SESSION_CNT</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 151,564/151,564 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6427,14 +6891,14 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6479,21 +6943,29 @@
           <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L103" s="6" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,223행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6538,21 +7010,29 @@
           <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
         </is>
       </c>
-      <c r="L104" s="6" t="inlineStr">
+      <c r="L104" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,223행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6597,21 +7077,29 @@
           <t>DIM_BIGQUERY_EVENT</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr"/>
-      <c r="J105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L105" s="6" t="inlineStr">
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,223행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6671,14 +7159,14 @@
           <t>2024 기념일 캠페인 / 2024 ACL 등</t>
         </is>
       </c>
-      <c r="L106" s="6" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6723,21 +7211,29 @@
           <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
         </is>
       </c>
-      <c r="L107" s="6" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 208행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6782,17 +7278,25 @@
           <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="6" t="inlineStr">
+      <c r="L108" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 208행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6840,7 +7344,7 @@
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr"/>
-      <c r="L109" s="6" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6899,7 +7403,7 @@
           <t>예) https://m.goodneighbors.kr/campaign/turn25b</t>
         </is>
       </c>
-      <c r="L110" s="6" t="inlineStr">
+      <c r="L110" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6951,17 +7455,25 @@
           <t>FBQ.SCROLL_DEPTH</t>
         </is>
       </c>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 30,323/151,564 (20.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7521,14 @@
       <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="5" t="inlineStr">
+      <c r="L112" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -7061,17 +7573,25 @@
           <t>DIM_BIGQUERY_SOURCE</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr"/>
-      <c r="J113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="K113" s="4" t="inlineStr"/>
-      <c r="L113" s="6" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 208행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7116,17 +7636,25 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr"/>
-      <c r="J114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="7" t="inlineStr">
+      <c r="L114" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7171,17 +7699,25 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I115" s="4" t="inlineStr"/>
-      <c r="J115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="7" t="inlineStr">
+      <c r="L115" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7226,17 +7762,25 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr"/>
-      <c r="J116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K116" s="4" t="inlineStr"/>
-      <c r="L116" s="6" t="inlineStr">
+      <c r="L116" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7281,21 +7825,29 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
           <t>신규: 당해년도 개발, 기존: 당해년도 이전 개발</t>
         </is>
       </c>
-      <c r="L117" s="7" t="inlineStr">
+      <c r="L117" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7340,17 +7892,25 @@
           <t>DIM_ORG</t>
         </is>
       </c>
-      <c r="I118" s="4" t="inlineStr"/>
-      <c r="J118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_ID</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
       <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="7" t="inlineStr">
+      <c r="L118" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7395,17 +7955,25 @@
           <t>DIM_ORG</t>
         </is>
       </c>
-      <c r="I119" s="4" t="inlineStr"/>
-      <c r="J119" s="4" t="inlineStr"/>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_ID</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
       <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="7" t="inlineStr">
+      <c r="L119" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7450,17 +8018,25 @@
           <t>DIM_ORG</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr"/>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_ID</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
       <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="7" t="inlineStr">
+      <c r="L120" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7516,14 +8092,14 @@
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="7" t="inlineStr">
+      <c r="L121" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7579,14 +8155,14 @@
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="7" t="inlineStr">
+      <c r="L122" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7642,14 +8218,14 @@
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="7" t="inlineStr">
+      <c r="L123" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7705,14 +8281,14 @@
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
-      <c r="L124" s="7" t="inlineStr">
+      <c r="L124" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7760,7 +8336,7 @@
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="7" t="inlineStr">
+      <c r="L125" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7812,14 +8388,22 @@
           <t>DIM_MEMBER_IDENTITY</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr"/>
-      <c r="J126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
           <t>"페이지 경로+쿼리 문자열"에서 파생. URL에서 childnum= 뒤에 오는 13자리. 예) https://gni.kr/url/25acl_25ABC.gn?memnum=1831636&amp;childnum=CMR-0102-002758 → 결연아동코드 = CMR-0102-002758</t>
         </is>
       </c>
-      <c r="L126" s="6" t="inlineStr">
+      <c r="L126" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7871,17 +8455,25 @@
           <t>DIM_SPONSORSHIP</t>
         </is>
       </c>
-      <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
       <c r="K127" s="4" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr">
+      <c r="L127" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7926,21 +8518,29 @@
           <t>DIM_SPONSORSHIP</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr"/>
-      <c r="J128" s="4" t="inlineStr"/>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
           <t>국내사단(국내아동권리보호사업(사단법인), 결식아동지원, 아동학대예방, 저소득가정지원), 국내사복(국내아동권리보호사업(사회복지법인), 국내사업, 좋은이웃(사복)), 결연(해외아동결연), 해외구호(희망학교지원사업, 해외교육지원사업, 보건의료지원사업, 식수위생지원사업, 재난구호지원사업, 해외지역개발지원사업), 기타(대북지원사업, 좋은이웃, 전체사업지원)</t>
         </is>
       </c>
-      <c r="L128" s="7" t="inlineStr">
+      <c r="L128" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7985,17 +8585,25 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+        </is>
+      </c>
       <c r="K129" s="4" t="inlineStr"/>
-      <c r="L129" s="7" t="inlineStr">
+      <c r="L129" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8040,17 +8648,25 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr"/>
-      <c r="J130" s="4" t="inlineStr"/>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+        </is>
+      </c>
       <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="7" t="inlineStr">
+      <c r="L130" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8714,7 @@
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr"/>
-      <c r="L131" s="7" t="inlineStr">
+      <c r="L131" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8153,7 +8769,7 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="7" t="inlineStr">
+      <c r="L132" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8208,7 +8824,7 @@
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr"/>
-      <c r="L133" s="7" t="inlineStr">
+      <c r="L133" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8260,17 +8876,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I134" s="4" t="inlineStr"/>
-      <c r="J134" s="4" t="inlineStr"/>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="7" t="inlineStr">
+      <c r="L134" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8315,17 +8939,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr"/>
-      <c r="J135" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="7" t="inlineStr">
+      <c r="L135" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8370,17 +9002,25 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr"/>
-      <c r="J136" s="4" t="inlineStr"/>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="7" t="inlineStr">
+      <c r="L136" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8425,17 +9065,25 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr"/>
-      <c r="J137" s="4" t="inlineStr"/>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K137" s="4" t="inlineStr"/>
-      <c r="L137" s="7" t="inlineStr">
+      <c r="L137" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8480,17 +9128,25 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr"/>
-      <c r="J138" s="4" t="inlineStr"/>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K138" s="4" t="inlineStr"/>
-      <c r="L138" s="7" t="inlineStr">
+      <c r="L138" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8535,17 +9191,25 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr"/>
-      <c r="J139" s="4" t="inlineStr"/>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="7" t="inlineStr">
+      <c r="L139" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8593,7 +9257,7 @@
       <c r="I140" s="4" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr"/>
-      <c r="L140" s="7" t="inlineStr">
+      <c r="L140" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8648,14 +9312,14 @@
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="7" t="inlineStr">
+      <c r="L141" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_DATE` 16,437행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8703,7 +9367,7 @@
       <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr"/>
-      <c r="L142" s="7" t="inlineStr">
+      <c r="L142" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8758,7 +9422,7 @@
       <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr"/>
-      <c r="L143" s="7" t="inlineStr">
+      <c r="L143" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8813,7 +9477,7 @@
       <c r="I144" s="4" t="inlineStr"/>
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr"/>
-      <c r="L144" s="7" t="inlineStr">
+      <c r="L144" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8868,7 +9532,7 @@
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="7" t="inlineStr">
+      <c r="L145" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8923,7 +9587,7 @@
       <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="7" t="inlineStr">
+      <c r="L146" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8978,7 +9642,7 @@
       <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr"/>
-      <c r="L147" s="7" t="inlineStr">
+      <c r="L147" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9033,7 +9697,7 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="7" t="inlineStr">
+      <c r="L148" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9088,7 +9752,7 @@
       <c r="I149" s="4" t="inlineStr"/>
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr"/>
-      <c r="L149" s="7" t="inlineStr">
+      <c r="L149" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9143,7 +9807,7 @@
       <c r="I150" s="4" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="7" t="inlineStr">
+      <c r="L150" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9206,14 +9870,14 @@
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
-      <c r="L151" s="7" t="inlineStr">
+      <c r="L151" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9922,25 @@
           <t>FME→FMM.DEV_MEMBERS</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr"/>
-      <c r="J152" s="4" t="inlineStr"/>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -9313,17 +9985,25 @@
           <t>FME→FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr"/>
-      <c r="J153" s="4" t="inlineStr"/>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K153" s="4" t="inlineStr"/>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -9368,17 +10048,25 @@
           <t>FME→FMM.INCREASE_MEMBERS</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr"/>
-      <c r="J154" s="4" t="inlineStr"/>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="5" t="inlineStr">
+      <c r="L154" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9423,17 +10111,25 @@
           <t>FME→FMM.INCREASE_CNT</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K155" s="4" t="inlineStr"/>
-      <c r="L155" s="5" t="inlineStr">
+      <c r="L155" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9481,7 +10177,7 @@
       <c r="I156" s="4" t="inlineStr"/>
       <c r="J156" s="4" t="inlineStr"/>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="5" t="inlineStr">
+      <c r="L156" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9536,7 +10232,7 @@
       <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="5" t="inlineStr">
+      <c r="L157" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9591,7 +10287,7 @@
       <c r="I158" s="4" t="inlineStr"/>
       <c r="J158" s="4" t="inlineStr"/>
       <c r="K158" s="4" t="inlineStr"/>
-      <c r="L158" s="5" t="inlineStr">
+      <c r="L158" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9646,7 +10342,7 @@
       <c r="I159" s="4" t="inlineStr"/>
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr"/>
-      <c r="L159" s="5" t="inlineStr">
+      <c r="L159" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9698,17 +10394,25 @@
           <t>FMM.ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr"/>
-      <c r="J160" s="4" t="inlineStr"/>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K160" s="4" t="inlineStr"/>
-      <c r="L160" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 38,423,126/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -9753,17 +10457,25 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr"/>
-      <c r="J161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -9808,10 +10520,18 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr"/>
-      <c r="J162" s="4" t="inlineStr"/>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="7" t="inlineStr">
+      <c r="L162" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9863,17 +10583,25 @@
           <t>FMM.ACTIVE_CUM_CNT</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr"/>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="5" t="inlineStr">
+      <c r="L163" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9921,7 +10649,7 @@
       <c r="I164" s="4" t="inlineStr"/>
       <c r="J164" s="4" t="inlineStr"/>
       <c r="K164" s="4" t="inlineStr"/>
-      <c r="L164" s="7" t="inlineStr">
+      <c r="L164" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9976,7 +10704,7 @@
       <c r="I165" s="4" t="inlineStr"/>
       <c r="J165" s="4" t="inlineStr"/>
       <c r="K165" s="4" t="inlineStr"/>
-      <c r="L165" s="7" t="inlineStr">
+      <c r="L165" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10028,17 +10756,25 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr"/>
-      <c r="J166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_ID</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
       <c r="K166" s="4" t="inlineStr"/>
-      <c r="L166" s="7" t="inlineStr">
+      <c r="L166" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -10083,14 +10819,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr"/>
-      <c r="J167" s="4" t="inlineStr"/>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
           <t>캠페인 가입 이후 납입하는 회비</t>
         </is>
       </c>
-      <c r="L167" s="7" t="inlineStr">
+      <c r="L167" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10149,7 +10893,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 개월수</t>
         </is>
       </c>
-      <c r="L168" s="7" t="inlineStr">
+      <c r="L168" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10208,7 +10952,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 년수</t>
         </is>
       </c>
-      <c r="L169" s="7" t="inlineStr">
+      <c r="L169" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10260,8 +11004,16 @@
           <t>SV metric — 분자: Σ(유지기간×DEV_MEMBERS) / 분모: DEV_MEMBERS(총)</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr"/>
-      <c r="J170" s="4" t="inlineStr"/>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
@@ -10269,12 +11021,12 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10326,7 +11078,7 @@
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
         </is>
       </c>
-      <c r="L171" s="7" t="inlineStr">
+      <c r="L171" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10385,7 +11137,7 @@
           <t>N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수</t>
         </is>
       </c>
-      <c r="L172" s="7" t="inlineStr">
+      <c r="L172" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10444,7 +11196,7 @@
           <t>(N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수) × 100</t>
         </is>
       </c>
-      <c r="L173" s="7" t="inlineStr">
+      <c r="L173" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10503,7 +11255,7 @@
           <t>평균 납입회비 × 평균 활동 기간</t>
         </is>
       </c>
-      <c r="L174" s="7" t="inlineStr">
+      <c r="L174" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10562,7 +11314,7 @@
           <t>광고비(편성비) 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L175" s="6" t="inlineStr">
+      <c r="L175" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -10614,21 +11366,29 @@
           <t>SV metric — 분자: FUNDRAISING_COST / 분모: DEV_CNT[신규]</t>
         </is>
       </c>
-      <c r="I176" s="4" t="inlineStr"/>
-      <c r="J176" s="4" t="inlineStr"/>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>ERP_BUDGET.EXEC_AMT</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>BDGT_ACMSLT_LEDGER</t>
+        </is>
+      </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
           <t>ERP 모금성 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L176" s="5" t="inlineStr">
+      <c r="L176" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BUDGET` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BUDGET.FUNDRAISING_COST` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -10673,8 +11433,16 @@
           <t>SV metric — 분자: PAID_FEE(또는 LTV) − 비용 / 분모: 비용(FBD)</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr"/>
-      <c r="J177" s="4" t="inlineStr"/>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
           <t>(총 수익−총 비용) / 총 비용 × 100</t>
@@ -10682,12 +11450,12 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10732,21 +11500,29 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr"/>
-      <c r="J178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
         </is>
       </c>
-      <c r="L178" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -10791,21 +11567,29 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr"/>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
         </is>
       </c>
-      <c r="L179" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -10850,21 +11634,29 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr"/>
-      <c r="J180" s="4" t="inlineStr"/>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
         </is>
       </c>
-      <c r="L180" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -10909,8 +11701,16 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr"/>
-      <c r="J181" s="4" t="inlineStr"/>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
           <t>캠페인별 중단(건) / (캠페인별 개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -10918,12 +11718,12 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10968,8 +11768,16 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr"/>
-      <c r="J182" s="4" t="inlineStr"/>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 중단(건) / (캠페인 개발(건) + 캠페인 전월말활동회원(건))</t>
@@ -10977,12 +11785,12 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11027,8 +11835,16 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I183" s="4" t="inlineStr"/>
-      <c r="J183" s="4" t="inlineStr"/>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
           <t>캠페인별 누계중단(건) / (캠페인별 누계개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -11036,12 +11852,12 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11086,8 +11902,16 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 누계중단(건) / 캠페인별 누계개발(건)</t>
@@ -11095,12 +11919,12 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11145,8 +11969,16 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I185" s="4" t="inlineStr"/>
-      <c r="J185" s="4" t="inlineStr"/>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 중단(건) / (캠페인별 납입방식 개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -11154,12 +11986,12 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11204,21 +12036,29 @@
           <t>FMM.CHURN_CNT</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr"/>
-      <c r="J186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
           <t>후원취소 및 감액한 후원사업의 금액 / 10,000</t>
         </is>
       </c>
-      <c r="L186" s="5" t="inlineStr">
+      <c r="L186" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11263,21 +12103,29 @@
           <t>SV metric — 분자: CHURN_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I187" s="4" t="inlineStr"/>
-      <c r="J187" s="4" t="inlineStr"/>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
           <t>캠페인별 이탈(건) / 캠페인별 개발(건)</t>
         </is>
       </c>
-      <c r="L187" s="5" t="inlineStr">
+      <c r="L187" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11322,8 +12170,16 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I188" s="4" t="inlineStr"/>
-      <c r="J188" s="4" t="inlineStr"/>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -11331,12 +12187,12 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11381,8 +12237,16 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I189" s="4" t="inlineStr"/>
-      <c r="J189" s="4" t="inlineStr"/>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -11390,12 +12254,12 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11440,8 +12304,16 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr"/>
-      <c r="J190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -11449,12 +12321,12 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11499,8 +12371,16 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I191" s="4" t="inlineStr"/>
-      <c r="J191" s="4" t="inlineStr"/>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -11508,12 +12388,12 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11558,8 +12438,16 @@
           <t>SV metric — 분자: PAID_FEE(캠페인) / 분모: PAID_FEE(전체)</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr"/>
-      <c r="J192" s="4" t="inlineStr"/>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입회비 / 총 납입회비 금액 × 100</t>
@@ -11567,12 +12455,12 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11617,21 +12505,29 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr"/>
-      <c r="J193" s="4" t="inlineStr"/>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L193" s="5" t="inlineStr">
+      <c r="L193" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11676,21 +12572,29 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I194" s="4" t="inlineStr"/>
-      <c r="J194" s="4" t="inlineStr"/>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L194" s="5" t="inlineStr">
+      <c r="L194" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11735,21 +12639,29 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT(캠페인) / 분모: CAMPAIGN_UNPAID_CNT(전체)</t>
         </is>
       </c>
-      <c r="I195" s="4" t="inlineStr"/>
-      <c r="J195" s="4" t="inlineStr"/>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비 / 총 미납회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L195" s="5" t="inlineStr">
+      <c r="L195" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11794,21 +12706,29 @@
           <t>SV metric — 분자: SEND_MEMBERS / 분모: 전체회원수(명)</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr"/>
-      <c r="J196" s="4" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
           <t>서비스별 발송수(명) / 전체회원수(명) × 100</t>
         </is>
       </c>
-      <c r="L196" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L196" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11853,8 +12773,16 @@
           <t>SV metric — 분자: SUCCESS_MEMBERS / 분모: SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I197" s="4" t="inlineStr"/>
-      <c r="J197" s="4" t="inlineStr"/>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
           <t>발송성공수(명) / 발송수(명) × 100</t>
@@ -11862,12 +12790,12 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11919,7 +12847,7 @@
           <t>클릭수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L198" s="6" t="inlineStr">
+      <c r="L198" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11971,8 +12899,16 @@
           <t>SV metric — 분자: DEV_MEMBERS / 분모: BigQuery 클릭회원(명)</t>
         </is>
       </c>
-      <c r="I199" s="4" t="inlineStr"/>
-      <c r="J199" s="4" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
           <t>개발회원(명) / 서비스 클릭수(명) × 100</t>
@@ -11980,12 +12916,12 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12973,7 @@
           <t>(증액 회원수(명,건) / 서비스별 발송 성공회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L200" s="7" t="inlineStr">
+      <c r="L200" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12096,7 +13032,7 @@
           <t>(서비스별 증액 후 N개월 시점 유지 회원(명,건) / 서비스별 증액 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L201" s="7" t="inlineStr">
+      <c r="L201" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12155,7 +13091,7 @@
           <t>(서비스별 발송 후 N개월 시점 유지 회원(명,건) / 서비스별 참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L202" s="7" t="inlineStr">
+      <c r="L202" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12214,7 +13150,7 @@
           <t>(서비스별 증액회원 중 납입회원(명,건) / 서비스별 증액회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 증액회원의 납입회비) / 서비스별 증액회원(명)</t>
         </is>
       </c>
-      <c r="L203" s="7" t="inlineStr">
+      <c r="L203" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12273,7 +13209,7 @@
           <t>(서비스별 참여회원 중 납입회원(명,건) / 서비스별 참여회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 참여회원의 납입회비) / 서비스별 참여회원(명)</t>
         </is>
       </c>
-      <c r="L204" s="7" t="inlineStr">
+      <c r="L204" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12332,7 +13268,7 @@
           <t>(서비스별 증액회원 중 중단회원(명,건) / 서비스별 증액회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L205" s="7" t="inlineStr">
+      <c r="L205" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12391,7 +13327,7 @@
           <t>(서비스별 참여회원 중 중단회원(명,건) / 서비스별 참여회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L206" s="7" t="inlineStr">
+      <c r="L206" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12450,7 +13386,7 @@
           <t>(해당 캠페인 서비스별 증액회원(명,건) / 서비스별 전체 증액회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L207" s="7" t="inlineStr">
+      <c r="L207" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12509,7 +13445,7 @@
           <t>(해당 캠페인 서비스별 참여회원(명,건) / 서비스별 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L208" s="7" t="inlineStr">
+      <c r="L208" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12568,7 +13504,7 @@
           <t>(해당 서비스·캠페인 조합에서 N개월 시점 유지 회원(명,건) / 해당 캠페인 가입회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L209" s="7" t="inlineStr">
+      <c r="L209" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12620,21 +13556,29 @@
           <t>SV metric — 분자: LETTER_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I210" s="4" t="inlineStr"/>
-      <c r="J210" s="4" t="inlineStr"/>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
           <t>(서비스별 서신 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L210" s="5" t="inlineStr">
+      <c r="L210" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -12686,7 +13630,7 @@
           <t>(서신참여 후 N개월 시점 유지 회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L211" s="7" t="inlineStr">
+      <c r="L211" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12745,7 +13689,7 @@
           <t>(서비스별 서신참여회원 중 납입회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 서신참여회원의 납입회비) / 서비스별 서신참여회원(명)</t>
         </is>
       </c>
-      <c r="L212" s="7" t="inlineStr">
+      <c r="L212" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12804,7 +13748,7 @@
           <t>(서비스별 서신참여회원 중 중단회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L213" s="7" t="inlineStr">
+      <c r="L213" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12863,7 +13807,7 @@
           <t>(해당 캠페인 서비스별 서신참여회원(명,건) / 서비스별 전체 서신참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L214" s="7" t="inlineStr">
+      <c r="L214" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12915,21 +13859,29 @@
           <t>SV metric — 분자: GIFT_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I215" s="4" t="inlineStr"/>
-      <c r="J215" s="4" t="inlineStr"/>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
           <t>(서비스별 선물금 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L215" s="5" t="inlineStr">
+      <c r="L215" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_SERVICE_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -12981,7 +13933,7 @@
           <t>(서비스별 선물금참여 후 N개월 시점 유지 회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L216" s="7" t="inlineStr">
+      <c r="L216" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13040,7 +13992,7 @@
           <t>(서비스별 선물금참여회원 중 납입회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 선물금참여회원의 납입회비) / 서비스별 선물금참여회원수(명)</t>
         </is>
       </c>
-      <c r="L217" s="7" t="inlineStr">
+      <c r="L217" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13099,7 +14051,7 @@
           <t>(서비스별 선물금참여회원 중 중단회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L218" s="7" t="inlineStr">
+      <c r="L218" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13158,7 +14110,7 @@
           <t>(해당 캠페인 서비스별 선물금참여회원(명,건) / 서비스별 전체 선물금참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L219" s="7" t="inlineStr">
+      <c r="L219" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13197,7 +14149,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -13398,7 +14350,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_MEMBER_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -16319,7 +17271,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -16446,7 +17398,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_MEMBER_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -17615,7 +18567,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_MEMBER_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -18514,7 +19466,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>FACT_DEV_ACHIEVEMENT.GOAL_CNT</t>
+          <t>FACT_MEMBER_DEV_ACHIEVEMENT.GOAL_CNT</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -20211,7 +21163,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -20301,7 +21253,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -20391,7 +21343,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -21271,7 +22223,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.JOIN_DATE</t>
+          <t>FACT_MEMBER_LIFECYCLE.JOIN_DATE</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -21314,7 +22266,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_DATE</t>
+          <t>FACT_MEMBER_LIFECYCLE.STOP_DATE</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -21744,7 +22696,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>SV metric — 누계 = base 의 YTD running sum (P7·물리 미저장) · base: FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>SV metric — 누계 = base 의 YTD running sum (P7·물리 미저장) · base: FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -22069,7 +23021,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -22515,7 +23467,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.UNPAID_STOP_MEMBERS</t>
+          <t>FACT_MEMBER_LIFECYCLE.UNPAID_STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -22558,7 +23510,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.UNPAID_STOP_CNT</t>
+          <t>FACT_MEMBER_LIFECYCLE.UNPAID_STOP_CNT</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25164,7 +26116,7 @@
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.DATE_SK</t>
+          <t>FACT_MESSAGE_DISPATCH.DATE_SK</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -25336,7 +26288,7 @@
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_TITLE</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_TITLE</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -25379,7 +26331,7 @@
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_TYPE</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_TYPE</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -25660,7 +26612,7 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.MEMBER_STOP_FLAG</t>
+          <t>FACT_MESSAGE_DISPATCH.MEMBER_STOP_FLAG</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -25746,7 +26698,7 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_STATUS</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_STATUS</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -25789,7 +26741,7 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_STATUS2</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_STATUS2</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -25832,7 +26784,7 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -26258,7 +27210,7 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.LETTER_PART_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -26301,7 +27253,7 @@
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.LETTER_PART_CNT</t>
+          <t>FACT_MESSAGE_DISPATCH.LETTER_PART_CNT</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -26344,7 +27296,7 @@
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.GIFT_PART_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -26387,7 +27339,7 @@
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.GIFT_PART_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -26430,7 +27382,7 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPATION_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPATION_TIMES</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -26645,7 +27597,7 @@
       </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.DATE_SK</t>
+          <t>FACT_MESSAGE_DISPATCH.DATE_SK</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -26817,7 +27769,7 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_TITLE</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_TITLE</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -26860,7 +27812,7 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_TYPE</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_TYPE</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -27149,7 +28101,7 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -28505,7 +29457,7 @@
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.DATE_SK</t>
+          <t>FACT_MESSAGE_DISPATCH.DATE_SK</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -28677,7 +29629,7 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_TITLE</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_TITLE</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -29329,7 +30281,7 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.MAIL_RECEIVE_FLAG</t>
+          <t>FACT_MESSAGE_DISPATCH.MAIL_RECEIVE_FLAG</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -29673,7 +30625,7 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.DATE_SK</t>
+          <t>FACT_MESSAGE_DISPATCH.DATE_SK</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -29845,7 +30797,7 @@
       </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_TITLE</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_TITLE</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -29888,7 +30840,7 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_TYPE</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_TYPE</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -30173,7 +31125,7 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.STOP_CHANNEL</t>
+          <t>FACT_MESSAGE_DISPATCH.STOP_CHANNEL</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -30427,7 +31379,7 @@
       </c>
       <c r="G333" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.REGULAR_DONATION</t>
+          <t>FACT_EVENT_ATTENDANCE.REGULAR_DONATION</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -30470,7 +31422,7 @@
       </c>
       <c r="G334" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.REGULAR_DONATION</t>
+          <t>FACT_EVENT_ATTENDANCE.REGULAR_DONATION</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -30513,7 +31465,7 @@
       </c>
       <c r="G335" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPATION_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPATION_TIMES</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -30556,7 +31508,7 @@
       </c>
       <c r="G336" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPATION_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPATION_TIMES</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -30599,7 +31551,7 @@
       </c>
       <c r="G337" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPATION_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPATION_TIMES</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -30685,7 +31637,7 @@
       </c>
       <c r="G339" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPANT_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPANT_CNT</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -30814,7 +31766,7 @@
       </c>
       <c r="G342" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_PATH</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -30857,7 +31809,7 @@
       </c>
       <c r="G343" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_PATH</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -30900,7 +31852,7 @@
       </c>
       <c r="G344" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_CHANNEL</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -30943,7 +31895,7 @@
       </c>
       <c r="G345" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_CHANNEL</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -30986,7 +31938,7 @@
       </c>
       <c r="G346" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.WIN_FLAG</t>
+          <t>FACT_EVENT_ATTENDANCE.WIN_FLAG</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -31533,7 +32485,7 @@
       </c>
       <c r="G359" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPATION_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPATION_TIMES</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -31619,7 +32571,7 @@
       </c>
       <c r="G361" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_CHANNEL</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -31662,7 +32614,7 @@
       </c>
       <c r="G362" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_PATH</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -31705,7 +32657,7 @@
       </c>
       <c r="G363" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_STATUS</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -32350,7 +33302,7 @@
       </c>
       <c r="G378" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.RECRUIT_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.RECRUIT_CNT</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -32393,7 +33345,7 @@
       </c>
       <c r="G379" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.TOTAL_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.TOTAL_CNT</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -32436,7 +33388,7 @@
       </c>
       <c r="G380" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.WAIT_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.WAIT_CNT</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -32479,7 +33431,7 @@
       </c>
       <c r="G381" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.CANCEL_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.CANCEL_CNT</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -32522,7 +33474,7 @@
       </c>
       <c r="G382" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.CONFIRM_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.CONFIRM_CNT</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -32565,7 +33517,7 @@
       </c>
       <c r="G383" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPATE_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPATE_CNT</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -32608,7 +33560,7 @@
       </c>
       <c r="G384" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.ABSENT_CNT</t>
+          <t>FACT_EVENT_ATTENDANCE.ABSENT_CNT</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -32858,7 +33810,7 @@
       </c>
       <c r="G390" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS</t>
+          <t>FACT_EVENT_ATTENDANCE.PART_STATUS</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -32901,7 +33853,7 @@
       </c>
       <c r="G391" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.SELF_PART_FLAG</t>
+          <t>FACT_EVENT_ATTENDANCE.SELF_PART_FLAG</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -33155,7 +34107,7 @@
       </c>
       <c r="G397" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.WAIT_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.WAIT_TIMES</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -33198,7 +34150,7 @@
       </c>
       <c r="G398" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.ABSENT_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.ABSENT_TIMES</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -33241,7 +34193,7 @@
       </c>
       <c r="G399" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTICIPATION_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.PARTICIPATION_TIMES</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -33284,7 +34236,7 @@
       </c>
       <c r="G400" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.CUM_APPLY_TIMES</t>
+          <t>FACT_EVENT_ATTENDANCE.CUM_APPLY_TIMES</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -33327,7 +34279,7 @@
       </c>
       <c r="G401" s="4" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.INCREASE_FLAG</t>
+          <t>FACT_EVENT_ATTENDANCE.INCREASE_FLAG</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
